--- a/excel_import/business_data_import_template.xlsx
+++ b/excel_import/business_data_import_template.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="12500" yWindow="600" windowWidth="25820" windowHeight="19260" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="4420" yWindow="1200" windowWidth="25820" windowHeight="19260" tabRatio="600" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
@@ -14,7 +14,7 @@
     <sheet name="Sotephwar_Inventory" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -864,7 +864,6 @@
           <t>2026-06-15 21:40:03</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3" ht="26" customHeight="1">
       <c r="A3" s="12" t="n">
@@ -911,7 +910,6 @@
           <t>2026-06-15 21:40:03</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4" ht="26" customHeight="1">
       <c r="A4" s="12" t="n">
@@ -958,7 +956,6 @@
           <t>2026-06-15 21:40:03</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5" ht="26" customHeight="1">
       <c r="A5" s="12" t="n">
@@ -1005,7 +1002,6 @@
           <t>2026-06-15 21:40:03</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6" ht="26" customHeight="1">
       <c r="A6" s="12" t="n">
@@ -1052,7 +1048,6 @@
           <t>2026-06-15 21:40:03</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="12" t="n">
@@ -1099,7 +1094,6 @@
           <t>2026-06-15 21:40:03</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8" ht="26" customHeight="1">
       <c r="A8" s="12" t="n">
@@ -1146,7 +1140,6 @@
           <t>2026-06-15 21:40:03</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9" ht="26" customHeight="1">
       <c r="A9" s="12" t="n">
@@ -1193,7 +1186,6 @@
           <t>2026-06-15 21:40:03</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr"/>
     </row>
     <row r="10" ht="26" customHeight="1">
       <c r="A10" s="12" t="n">
@@ -1240,7 +1232,6 @@
           <t>2026-06-15 21:40:03</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="12" t="n">
@@ -1287,7 +1278,6 @@
           <t>2026-06-15 21:40:03</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12" ht="26" customHeight="1">
       <c r="A12" s="12" t="n">
@@ -1334,7 +1324,6 @@
           <t>2026-06-15 21:40:03</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr"/>
     </row>
     <row r="13" ht="26" customHeight="1">
       <c r="A13" s="12" t="n">
@@ -1381,7 +1370,6 @@
           <t>2026-06-15 21:40:03</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr"/>
     </row>
     <row r="14" ht="26" customHeight="1">
       <c r="A14" s="12" t="n">
@@ -1428,7 +1416,6 @@
           <t>2026-06-15 21:40:03</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr"/>
     </row>
     <row r="15" ht="26" customHeight="1">
       <c r="A15" s="12" t="n">
@@ -1475,7 +1462,6 @@
           <t>2026-06-15 21:40:03</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr"/>
     </row>
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="12" t="n">
@@ -1522,7 +1508,6 @@
           <t>2026-06-15 21:40:03</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr"/>
     </row>
     <row r="17" ht="26" customHeight="1">
       <c r="A17" s="12" t="n">
@@ -1569,7 +1554,6 @@
           <t>2026-06-15 21:40:03</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr"/>
     </row>
     <row r="18" ht="26" customHeight="1">
       <c r="A18" s="12" t="n">
@@ -1616,7 +1600,6 @@
           <t>2026-06-15 21:40:03</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr"/>
     </row>
     <row r="19" ht="26" customHeight="1">
       <c r="A19" s="12" t="n">
@@ -1663,7 +1646,6 @@
           <t>2026-06-15 21:40:03</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr"/>
     </row>
     <row r="20" ht="26" customHeight="1">
       <c r="A20" s="12" t="n">
@@ -1710,7 +1692,6 @@
           <t>2026-06-15 21:40:03</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr"/>
     </row>
     <row r="21" ht="26" customHeight="1">
       <c r="A21" s="12" t="n">
@@ -1757,7 +1738,6 @@
           <t>2026-06-15 21:40:03</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr"/>
     </row>
     <row r="22" ht="26" customHeight="1">
       <c r="A22" s="12" t="n">
@@ -1804,7 +1784,6 @@
           <t>2026-06-15 21:40:03</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr"/>
     </row>
     <row r="23" ht="26" customHeight="1">
       <c r="A23" s="12" t="n">
@@ -1851,7 +1830,6 @@
           <t>2026-06-15 21:40:03</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr"/>
     </row>
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="12" t="n">
@@ -1898,7 +1876,6 @@
           <t>2026-06-15 21:40:03</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr"/>
     </row>
     <row r="25" ht="26" customHeight="1">
       <c r="A25" s="12" t="n">
@@ -1945,7 +1922,6 @@
           <t>2026-06-15 21:40:03</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr"/>
     </row>
     <row r="26" ht="26" customHeight="1">
       <c r="A26" s="12" t="n">
@@ -1992,7 +1968,6 @@
           <t>2026-06-15 21:40:03</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr"/>
     </row>
     <row r="27" ht="26" customHeight="1">
       <c r="A27" s="12" t="n">
@@ -2039,7 +2014,6 @@
           <t>2026-06-15 21:40:03</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr"/>
     </row>
     <row r="28" ht="26" customHeight="1">
       <c r="A28" s="12" t="n">
@@ -2086,7 +2060,6 @@
           <t>2026-06-15 21:40:03</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr"/>
     </row>
     <row r="29" ht="26" customHeight="1">
       <c r="A29" s="12" t="n">
@@ -2133,7 +2106,6 @@
           <t>2026-06-15 21:40:03</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr"/>
     </row>
     <row r="30" ht="26" customHeight="1">
       <c r="A30" s="12" t="n">
@@ -2180,7 +2152,6 @@
           <t>2026-06-15 21:40:03</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr"/>
     </row>
     <row r="31" ht="26" customHeight="1">
       <c r="A31" s="12" t="n">
@@ -2227,7 +2198,6 @@
           <t>2026-06-15 21:40:03</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr"/>
     </row>
     <row r="32" ht="26" customHeight="1">
       <c r="A32" s="12" t="n">
@@ -2274,7 +2244,6 @@
           <t>2026-06-15 21:40:03</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr"/>
     </row>
     <row r="33" ht="26" customHeight="1">
       <c r="A33" s="12" t="n">
@@ -2321,7 +2290,6 @@
           <t>2026-06-15 21:40:03</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr"/>
     </row>
     <row r="34" ht="26" customHeight="1">
       <c r="A34" s="12" t="n">
@@ -2368,7 +2336,6 @@
           <t>2026-06-15 21:40:03</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr"/>
     </row>
     <row r="35" ht="26" customHeight="1">
       <c r="A35" s="12" t="n">
@@ -2415,7 +2382,6 @@
           <t>2026-06-15 21:40:03</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr"/>
     </row>
     <row r="36" ht="26" customHeight="1">
       <c r="A36" s="12" t="n">
@@ -2462,7 +2428,6 @@
           <t>2026-06-15 21:40:03</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr"/>
     </row>
     <row r="37" ht="26" customHeight="1">
       <c r="A37" s="12" t="n">
@@ -2509,7 +2474,6 @@
           <t>2026-06-15 21:40:03</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr"/>
     </row>
     <row r="38" ht="26" customHeight="1">
       <c r="A38" s="12" t="n">
@@ -2556,7 +2520,6 @@
           <t>2026-06-15 21:40:03</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr"/>
     </row>
     <row r="39" ht="26" customHeight="1">
       <c r="A39" s="12" t="n">
@@ -2603,7 +2566,6 @@
           <t>2026-06-15 21:40:03</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr"/>
     </row>
     <row r="40" ht="26" customHeight="1">
       <c r="A40" s="12" t="n">
@@ -2650,7 +2612,6 @@
           <t>2026-06-15 21:40:03</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr"/>
     </row>
     <row r="41" ht="26" customHeight="1">
       <c r="A41" s="12" t="n">
@@ -2697,7 +2658,6 @@
           <t>2026-06-15 21:40:03</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr"/>
     </row>
     <row r="42" ht="26" customHeight="1">
       <c r="A42" s="12" t="n">
@@ -2744,7 +2704,6 @@
           <t>2026-06-15 21:40:03</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr"/>
     </row>
     <row r="43" ht="26" customHeight="1">
       <c r="A43" s="12" t="n">
@@ -2791,7 +2750,6 @@
           <t>2026-06-15 21:40:03</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr"/>
     </row>
     <row r="44" ht="26" customHeight="1">
       <c r="A44" s="12" t="n">
@@ -2838,7 +2796,6 @@
           <t>2026-06-15 21:40:03</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr"/>
     </row>
     <row r="45" ht="26" customHeight="1">
       <c r="A45" s="12" t="n">
@@ -2885,7 +2842,6 @@
           <t>2026-06-15 21:40:03</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr"/>
     </row>
     <row r="46" ht="26" customHeight="1">
       <c r="A46" s="12" t="n">
@@ -2932,7 +2888,6 @@
           <t>2026-06-15 21:40:03</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr"/>
     </row>
     <row r="47" ht="26" customHeight="1">
       <c r="A47" s="12" t="n">
@@ -2979,7 +2934,6 @@
           <t>2026-06-15 21:40:03</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr"/>
     </row>
     <row r="48" ht="26" customHeight="1">
       <c r="A48" s="12" t="n">
@@ -3026,7 +2980,6 @@
           <t>2026-06-15 21:40:03</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr"/>
     </row>
     <row r="49" ht="26" customHeight="1">
       <c r="A49" s="12" t="n">
@@ -3071,7 +3024,6 @@
           <t>2026-06-15 21:40:03</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr"/>
     </row>
     <row r="50" ht="26" customHeight="1">
       <c r="A50" s="12" t="n">
@@ -3118,7 +3070,6 @@
           <t>2026-06-15 21:40:03</t>
         </is>
       </c>
-      <c r="M50" t="inlineStr"/>
     </row>
     <row r="51" ht="26" customHeight="1">
       <c r="A51" s="12" t="n">
@@ -3165,7 +3116,6 @@
           <t>2026-06-15 21:40:03</t>
         </is>
       </c>
-      <c r="M51" t="inlineStr"/>
     </row>
     <row r="52" ht="26" customHeight="1">
       <c r="A52" s="12" t="n">
@@ -3212,7 +3162,6 @@
           <t>2026-06-15 21:40:03</t>
         </is>
       </c>
-      <c r="M52" t="inlineStr"/>
     </row>
     <row r="53" ht="26" customHeight="1">
       <c r="A53" s="12" t="n">
@@ -3259,7 +3208,6 @@
           <t>2026-06-15 21:40:03</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr"/>
     </row>
     <row r="54" ht="26" customHeight="1">
       <c r="A54" s="12" t="n">
@@ -3306,7 +3254,6 @@
           <t>2026-06-15 21:40:03</t>
         </is>
       </c>
-      <c r="M54" t="inlineStr"/>
     </row>
     <row r="55" ht="26" customHeight="1">
       <c r="A55" s="12" t="n">
@@ -3353,7 +3300,6 @@
           <t>2026-06-15 21:40:03</t>
         </is>
       </c>
-      <c r="M55" t="inlineStr"/>
     </row>
     <row r="56" ht="26" customHeight="1">
       <c r="A56" s="12" t="n">
@@ -3400,7 +3346,6 @@
           <t>2026-06-15 21:40:03</t>
         </is>
       </c>
-      <c r="M56" t="inlineStr"/>
     </row>
     <row r="57" ht="26" customHeight="1">
       <c r="A57" s="12" t="n">
@@ -3447,7 +3392,6 @@
           <t>2026-06-15 21:40:03</t>
         </is>
       </c>
-      <c r="M57" t="inlineStr"/>
     </row>
     <row r="58" ht="26" customHeight="1">
       <c r="A58" s="12" t="n">
@@ -3494,7 +3438,6 @@
           <t>2026-06-15 21:40:03</t>
         </is>
       </c>
-      <c r="M58" t="inlineStr"/>
     </row>
     <row r="59" ht="26" customHeight="1">
       <c r="A59" s="12" t="n">
@@ -3541,7 +3484,6 @@
           <t>2026-06-15 21:40:03</t>
         </is>
       </c>
-      <c r="M59" t="inlineStr"/>
     </row>
     <row r="60" ht="26" customHeight="1">
       <c r="A60" s="12" t="n">
@@ -3588,7 +3530,6 @@
           <t>2026-06-15 21:40:03</t>
         </is>
       </c>
-      <c r="M60" t="inlineStr"/>
     </row>
     <row r="61" ht="26" customHeight="1">
       <c r="A61" s="12" t="n">
@@ -3635,7 +3576,6 @@
           <t>2026-06-15 21:40:03</t>
         </is>
       </c>
-      <c r="M61" t="inlineStr"/>
     </row>
     <row r="62" ht="26" customHeight="1">
       <c r="A62" s="12" t="n">
@@ -3682,7 +3622,6 @@
           <t>2026-06-15 21:40:03</t>
         </is>
       </c>
-      <c r="M62" t="inlineStr"/>
     </row>
     <row r="63" ht="26" customHeight="1">
       <c r="A63" s="12" t="n">
@@ -3729,7 +3668,6 @@
           <t>2026-06-15 21:40:03</t>
         </is>
       </c>
-      <c r="M63" t="inlineStr"/>
     </row>
     <row r="64" ht="26" customHeight="1">
       <c r="A64" s="12" t="n">
@@ -3776,7 +3714,6 @@
           <t>2026-06-15 21:40:03</t>
         </is>
       </c>
-      <c r="M64" t="inlineStr"/>
     </row>
     <row r="65" ht="26" customHeight="1">
       <c r="A65" s="12" t="n">
@@ -3823,7 +3760,6 @@
           <t>2026-06-15 21:40:03</t>
         </is>
       </c>
-      <c r="M65" t="inlineStr"/>
     </row>
     <row r="66" ht="26" customHeight="1">
       <c r="A66" s="12" t="n">
@@ -3870,7 +3806,6 @@
           <t>2026-06-15 21:40:03</t>
         </is>
       </c>
-      <c r="M66" t="inlineStr"/>
     </row>
     <row r="67" ht="26" customHeight="1">
       <c r="A67" s="12" t="n">
@@ -3917,7 +3852,6 @@
           <t>2026-06-15 21:40:03</t>
         </is>
       </c>
-      <c r="M67" t="inlineStr"/>
     </row>
     <row r="68" ht="26" customHeight="1">
       <c r="A68" s="12" t="n">
@@ -3964,7 +3898,6 @@
           <t>2026-06-15 21:40:03</t>
         </is>
       </c>
-      <c r="M68" t="inlineStr"/>
     </row>
     <row r="69" ht="26" customHeight="1">
       <c r="A69" s="12" t="n">
@@ -4011,7 +3944,6 @@
           <t>2026-06-15 21:40:03</t>
         </is>
       </c>
-      <c r="M69" t="inlineStr"/>
     </row>
     <row r="70" ht="26" customHeight="1">
       <c r="A70" s="12" t="n">
@@ -4058,7 +3990,6 @@
           <t>2026-06-15 21:40:03</t>
         </is>
       </c>
-      <c r="M70" t="inlineStr"/>
     </row>
     <row r="71" ht="26" customHeight="1">
       <c r="A71" s="12" t="n">
@@ -4105,7 +4036,6 @@
           <t>2026-06-15 21:40:03</t>
         </is>
       </c>
-      <c r="M71" t="inlineStr"/>
     </row>
     <row r="72" ht="26" customHeight="1">
       <c r="A72" s="12" t="n">
@@ -4152,7 +4082,6 @@
           <t>2026-06-15 21:40:03</t>
         </is>
       </c>
-      <c r="M72" t="inlineStr"/>
     </row>
     <row r="73" ht="26" customHeight="1">
       <c r="A73" s="12" t="n">
@@ -4199,7 +4128,6 @@
           <t>2026-06-15 21:40:03</t>
         </is>
       </c>
-      <c r="M73" t="inlineStr"/>
     </row>
     <row r="74" ht="26" customHeight="1">
       <c r="A74" s="12" t="n">
@@ -4246,7 +4174,6 @@
           <t>2026-06-15 21:40:03</t>
         </is>
       </c>
-      <c r="M74" t="inlineStr"/>
     </row>
     <row r="75" ht="26" customHeight="1">
       <c r="A75" s="12" t="n">
@@ -4293,7 +4220,6 @@
           <t>2026-06-15 21:40:03</t>
         </is>
       </c>
-      <c r="M75" t="inlineStr"/>
     </row>
     <row r="76" ht="26" customHeight="1">
       <c r="A76" s="12" t="n">
@@ -4340,7 +4266,6 @@
           <t>2026-06-15 21:40:03</t>
         </is>
       </c>
-      <c r="M76" t="inlineStr"/>
     </row>
     <row r="77" ht="26" customHeight="1">
       <c r="A77" s="12" t="n">
@@ -4387,7 +4312,6 @@
           <t>2026-06-15 21:40:03</t>
         </is>
       </c>
-      <c r="M77" t="inlineStr"/>
     </row>
     <row r="78" ht="26" customHeight="1">
       <c r="A78" s="12" t="n">
@@ -4434,7 +4358,6 @@
           <t>2026-06-15 21:40:03</t>
         </is>
       </c>
-      <c r="M78" t="inlineStr"/>
     </row>
     <row r="79" ht="26" customHeight="1">
       <c r="A79" s="12" t="n">
@@ -4481,7 +4404,6 @@
           <t>2026-06-15 21:40:03</t>
         </is>
       </c>
-      <c r="M79" t="inlineStr"/>
     </row>
     <row r="80" ht="26" customHeight="1">
       <c r="A80" s="12" t="n">
@@ -4528,7 +4450,6 @@
           <t>2026-06-15 21:40:03</t>
         </is>
       </c>
-      <c r="M80" t="inlineStr"/>
     </row>
     <row r="81" ht="26" customHeight="1">
       <c r="A81" s="12" t="n">
@@ -4575,7 +4496,6 @@
           <t>2026-06-15 21:40:03</t>
         </is>
       </c>
-      <c r="M81" t="inlineStr"/>
     </row>
     <row r="82" ht="26" customHeight="1">
       <c r="A82" s="12" t="n">
@@ -4622,7 +4542,6 @@
           <t>2026-06-15 21:40:03</t>
         </is>
       </c>
-      <c r="M82" t="inlineStr"/>
     </row>
     <row r="83" ht="26" customHeight="1">
       <c r="A83" s="12" t="n">
@@ -4669,7 +4588,6 @@
           <t>2026-06-15 21:40:03</t>
         </is>
       </c>
-      <c r="M83" t="inlineStr"/>
     </row>
     <row r="84" ht="26" customHeight="1">
       <c r="A84" s="12" t="n">
@@ -4716,7 +4634,6 @@
           <t>2026-06-15 21:40:03</t>
         </is>
       </c>
-      <c r="M84" t="inlineStr"/>
     </row>
     <row r="85" ht="26" customHeight="1">
       <c r="A85" s="12" t="n">
@@ -4763,7 +4680,6 @@
           <t>2026-06-15 21:40:03</t>
         </is>
       </c>
-      <c r="M85" t="inlineStr"/>
     </row>
     <row r="86" ht="26" customHeight="1">
       <c r="A86" s="12" t="n">
@@ -4810,7 +4726,6 @@
           <t>2026-06-15 21:40:03</t>
         </is>
       </c>
-      <c r="M86" t="inlineStr"/>
     </row>
     <row r="87" ht="26" customHeight="1">
       <c r="A87" s="12" t="n">
@@ -4857,7 +4772,6 @@
           <t>2026-06-15 21:40:03</t>
         </is>
       </c>
-      <c r="M87" t="inlineStr"/>
     </row>
     <row r="88" ht="26" customHeight="1">
       <c r="A88" s="12" t="n">
@@ -4904,7 +4818,6 @@
           <t>2026-06-15 21:40:03</t>
         </is>
       </c>
-      <c r="M88" t="inlineStr"/>
     </row>
     <row r="89" ht="26" customHeight="1">
       <c r="A89" s="12" t="n">
@@ -4951,7 +4864,6 @@
           <t>2026-06-15 21:40:03</t>
         </is>
       </c>
-      <c r="M89" t="inlineStr"/>
     </row>
     <row r="90" ht="26" customHeight="1">
       <c r="A90" s="12" t="n">
@@ -4998,7 +4910,6 @@
           <t>2026-06-15 21:40:03</t>
         </is>
       </c>
-      <c r="M90" t="inlineStr"/>
     </row>
     <row r="91" ht="26" customHeight="1">
       <c r="A91" s="12" t="n">
@@ -5045,7 +4956,6 @@
           <t>2026-06-15 21:40:03</t>
         </is>
       </c>
-      <c r="M91" t="inlineStr"/>
     </row>
     <row r="92" ht="26" customHeight="1">
       <c r="A92" s="12" t="n">
@@ -5092,7 +5002,6 @@
           <t>2026-06-15 21:40:03</t>
         </is>
       </c>
-      <c r="M92" t="inlineStr"/>
     </row>
     <row r="93" ht="26" customHeight="1">
       <c r="A93" s="12" t="n">
@@ -5139,7 +5048,6 @@
           <t>2026-06-15 21:40:03</t>
         </is>
       </c>
-      <c r="M93" t="inlineStr"/>
     </row>
     <row r="94" ht="26" customHeight="1">
       <c r="A94" s="12" t="n">
@@ -5186,7 +5094,6 @@
           <t>2026-06-15 21:40:03</t>
         </is>
       </c>
-      <c r="M94" t="inlineStr"/>
     </row>
     <row r="95" ht="26" customHeight="1">
       <c r="A95" s="12" t="n">
@@ -5233,7 +5140,6 @@
           <t>2026-06-15 21:40:03</t>
         </is>
       </c>
-      <c r="M95" t="inlineStr"/>
     </row>
     <row r="96" ht="26" customHeight="1">
       <c r="A96" s="12" t="n">
@@ -5280,7 +5186,6 @@
           <t>2026-06-15 21:40:03</t>
         </is>
       </c>
-      <c r="M96" t="inlineStr"/>
     </row>
     <row r="97" ht="26" customHeight="1">
       <c r="A97" s="12" t="n">
@@ -5327,7 +5232,6 @@
           <t>2026-06-15 21:40:03</t>
         </is>
       </c>
-      <c r="M97" t="inlineStr"/>
     </row>
     <row r="98" ht="26" customHeight="1">
       <c r="A98" s="12" t="n">
@@ -5374,7 +5278,6 @@
           <t>2026-06-15 21:40:03</t>
         </is>
       </c>
-      <c r="M98" t="inlineStr"/>
     </row>
     <row r="99" ht="26" customHeight="1">
       <c r="A99" s="12" t="n">
@@ -5421,7 +5324,6 @@
           <t>2026-06-15 21:40:03</t>
         </is>
       </c>
-      <c r="M99" t="inlineStr"/>
     </row>
     <row r="100" ht="26" customHeight="1">
       <c r="A100" s="12" t="n">
@@ -5468,7 +5370,6 @@
           <t>2026-06-15 21:40:03</t>
         </is>
       </c>
-      <c r="M100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="12" t="n">
@@ -5515,7 +5416,6 @@
           <t>2026-06-15 21:40:03</t>
         </is>
       </c>
-      <c r="M101" t="inlineStr"/>
     </row>
     <row r="102" ht="26" customHeight="1">
       <c r="A102" s="12" t="n">
@@ -5562,7 +5462,6 @@
           <t>2026-06-15 21:40:03</t>
         </is>
       </c>
-      <c r="M102" t="inlineStr"/>
     </row>
     <row r="103" ht="26" customHeight="1">
       <c r="A103" s="12" t="n">
@@ -5609,7 +5508,6 @@
           <t>2026-06-15 21:40:03</t>
         </is>
       </c>
-      <c r="M103" t="inlineStr"/>
     </row>
     <row r="104" ht="26" customHeight="1">
       <c r="A104" s="12" t="n">
@@ -5656,7 +5554,6 @@
           <t>2026-06-15 21:40:03</t>
         </is>
       </c>
-      <c r="M104" t="inlineStr"/>
     </row>
     <row r="105" ht="26" customHeight="1">
       <c r="A105" s="12" t="n">
@@ -5703,7 +5600,6 @@
           <t>2026-06-15 21:40:03</t>
         </is>
       </c>
-      <c r="M105" t="inlineStr"/>
     </row>
     <row r="106" ht="26" customHeight="1">
       <c r="A106" s="12" t="n">
@@ -5750,7 +5646,6 @@
           <t>2026-06-15 21:40:03</t>
         </is>
       </c>
-      <c r="M106" t="inlineStr"/>
     </row>
     <row r="107" ht="26" customHeight="1">
       <c r="A107" s="12" t="n">
@@ -5797,7 +5692,6 @@
           <t>2026-06-15 21:40:03</t>
         </is>
       </c>
-      <c r="M107" t="inlineStr"/>
     </row>
     <row r="108" ht="26" customHeight="1">
       <c r="A108" s="12" t="n">
@@ -5844,7 +5738,6 @@
           <t>2026-06-15 21:40:03</t>
         </is>
       </c>
-      <c r="M108" t="inlineStr"/>
     </row>
     <row r="109" ht="26" customHeight="1">
       <c r="A109" s="12" t="n">
@@ -5891,7 +5784,6 @@
           <t>2026-06-15 21:40:03</t>
         </is>
       </c>
-      <c r="M109" t="inlineStr"/>
     </row>
     <row r="110" ht="26" customHeight="1">
       <c r="A110" s="12" t="n">
@@ -5938,7 +5830,6 @@
           <t>2026-06-15 21:40:03</t>
         </is>
       </c>
-      <c r="M110" t="inlineStr"/>
     </row>
     <row r="111" ht="26" customHeight="1">
       <c r="A111" s="16" t="n"/>
@@ -12750,256 +12641,1788 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="6" t="n"/>
-      <c r="D47" s="9" t="n"/>
-      <c r="E47" s="9" t="n"/>
+      <c r="A47" s="6" t="n">
+        <v>52</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Sote Phwar 1 L</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>200</v>
+      </c>
+      <c r="D47" s="9" t="n">
+        <v>6600000</v>
+      </c>
+      <c r="E47" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="F47" s="9" t="n"/>
+      <c r="H47" s="5" t="n">
+        <v>46187</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Kaung Kyaw</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="L47" t="n">
+        <v>685</v>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>2026-06-19 14:23:24</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="6" t="n"/>
-      <c r="D48" s="9" t="n"/>
-      <c r="E48" s="9" t="n"/>
+      <c r="A48" s="6" t="n">
+        <v>52</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Sote Phwar 4L</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>20</v>
+      </c>
+      <c r="D48" s="9" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="E48" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="F48" s="9" t="n"/>
+      <c r="H48" s="5" t="n">
+        <v>46187</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Kaung Kyaw</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="L48" t="n">
+        <v>686</v>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>2026-06-19 14:23:24</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="6" t="n"/>
-      <c r="D49" s="9" t="n"/>
-      <c r="E49" s="9" t="n"/>
+      <c r="A49" s="6" t="n">
+        <v>53</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Sote Phwar 4L</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>4</v>
+      </c>
+      <c r="D49" s="9" t="n">
+        <v>500000</v>
+      </c>
+      <c r="E49" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="F49" s="9" t="n"/>
+      <c r="H49" s="5" t="n">
+        <v>46187</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Khin Mar Lwin,Daw</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="L49" t="n">
+        <v>687</v>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>2026-06-19 14:23:24</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="6" t="n"/>
-      <c r="D50" s="9" t="n"/>
-      <c r="E50" s="9" t="n"/>
+      <c r="A50" s="6" t="n">
+        <v>54</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Sote Phwar 1 L</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>200</v>
+      </c>
+      <c r="D50" s="9" t="n">
+        <v>6600000</v>
+      </c>
+      <c r="E50" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="F50" s="9" t="n"/>
+      <c r="H50" s="5" t="n">
+        <v>46187</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Zun Ei Khaing</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="L50" t="n">
+        <v>688</v>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>2026-06-19 14:23:24</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="6" t="n"/>
-      <c r="D51" s="9" t="n"/>
-      <c r="E51" s="9" t="n"/>
+      <c r="A51" s="6" t="n">
+        <v>54</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Sote Phwar 4L</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>8</v>
+      </c>
+      <c r="D51" s="9" t="n">
+        <v>960000</v>
+      </c>
+      <c r="E51" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="F51" s="9" t="n"/>
+      <c r="H51" s="5" t="n">
+        <v>46187</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Zun Ei Khaing</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="L51" t="n">
+        <v>689</v>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>2026-06-19 14:23:24</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="6" t="n"/>
-      <c r="D52" s="9" t="n"/>
-      <c r="E52" s="9" t="n"/>
+      <c r="A52" s="6" t="n">
+        <v>55</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Sote Phwar 1 L</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>210</v>
+      </c>
+      <c r="D52" s="9" t="n">
+        <v>6600000</v>
+      </c>
+      <c r="E52" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="F52" s="9" t="n"/>
+      <c r="H52" s="5" t="n">
+        <v>46187</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Laye Yar Myay</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="L52" t="n">
+        <v>690</v>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>2026-06-19 14:23:24</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="6" t="n"/>
-      <c r="D53" s="9" t="n"/>
-      <c r="E53" s="9" t="n"/>
+      <c r="A53" s="6" t="n">
+        <v>56</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Sote Phwar 1 L</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>10</v>
+      </c>
+      <c r="D53" s="9" t="n">
+        <v>330000</v>
+      </c>
+      <c r="E53" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="F53" s="9" t="n"/>
+      <c r="H53" s="5" t="n">
+        <v>46187</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>ZLP</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="L53" t="n">
+        <v>691</v>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>2026-06-19 14:23:24</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="6" t="n"/>
-      <c r="D54" s="9" t="n"/>
-      <c r="E54" s="9" t="n"/>
+      <c r="A54" s="6" t="n">
+        <v>56</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Sote Phwar 500 mL</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>20</v>
+      </c>
+      <c r="D54" s="9" t="n">
+        <v>340000</v>
+      </c>
+      <c r="E54" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="F54" s="9" t="n"/>
+      <c r="H54" s="5" t="n">
+        <v>46187</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>ZLP</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="L54" t="n">
+        <v>692</v>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>2026-06-19 14:23:24</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="6" t="n"/>
-      <c r="D55" s="9" t="n"/>
-      <c r="E55" s="9" t="n"/>
-      <c r="F55" s="9" t="n"/>
+      <c r="A55" s="6" t="n">
+        <v>58</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Sote Phwar 1 L</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>1100</v>
+      </c>
+      <c r="D55" s="9" t="n">
+        <v>32500000</v>
+      </c>
+      <c r="E55" s="9" t="n">
+        <v>32500000</v>
+      </c>
+      <c r="F55" s="9" t="inlineStr">
+        <is>
+          <t>14.6.2026 Paid MM&amp;17.6.2026 Paid MM</t>
+        </is>
+      </c>
+      <c r="H55" s="5" t="n">
+        <v>46188</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Lucky 7</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="L55" t="n">
+        <v>693</v>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>2026-06-19 14:23:24</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="6" t="n"/>
-      <c r="D56" s="9" t="n"/>
-      <c r="E56" s="9" t="n"/>
-      <c r="F56" s="9" t="n"/>
+      <c r="A56" s="6" t="n">
+        <v>58</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Sote Phwar 500 mL</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>300</v>
+      </c>
+      <c r="D56" s="9" t="n">
+        <v>5100000</v>
+      </c>
+      <c r="E56" s="9" t="n">
+        <v>5100000</v>
+      </c>
+      <c r="F56" s="9" t="inlineStr">
+        <is>
+          <t>14.6.2026 Paid MM</t>
+        </is>
+      </c>
+      <c r="H56" s="5" t="n">
+        <v>46188</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Lucky 7</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="L56" t="n">
+        <v>694</v>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>2026-06-19 14:23:24</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="6" t="n"/>
-      <c r="D57" s="9" t="n"/>
-      <c r="E57" s="9" t="n"/>
-      <c r="F57" s="9" t="n"/>
+      <c r="A57" s="6" t="n">
+        <v>59</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Sote Phwar 1 L</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>1100</v>
+      </c>
+      <c r="D57" s="9" t="n">
+        <v>32500000</v>
+      </c>
+      <c r="E57" s="9" t="n">
+        <v>32500000</v>
+      </c>
+      <c r="F57" s="9" t="inlineStr">
+        <is>
+          <t>17.6.2026 Paid MM</t>
+        </is>
+      </c>
+      <c r="H57" s="5" t="n">
+        <v>46188</v>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Mya Yadanar</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="L57" t="n">
+        <v>695</v>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>2026-06-19 14:23:24</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="6" t="n"/>
-      <c r="D58" s="9" t="n"/>
-      <c r="E58" s="9" t="n"/>
-      <c r="F58" s="9" t="n"/>
+      <c r="A58" s="6" t="n">
+        <v>59</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Sote Phwar 500 mL</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>400</v>
+      </c>
+      <c r="D58" s="9" t="n">
+        <v>6800000</v>
+      </c>
+      <c r="E58" s="9" t="n">
+        <v>6800000</v>
+      </c>
+      <c r="F58" s="9" t="inlineStr">
+        <is>
+          <t>17.6.2026 Paid MM</t>
+        </is>
+      </c>
+      <c r="H58" s="5" t="n">
+        <v>46188</v>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Mya Yadanar</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="L58" t="n">
+        <v>696</v>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>2026-06-19 14:23:24</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="6" t="n"/>
-      <c r="D59" s="9" t="n"/>
-      <c r="E59" s="9" t="n"/>
+      <c r="A59" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Sote Phwar 4L</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>4</v>
+      </c>
+      <c r="D59" s="9" t="n">
+        <v>500000</v>
+      </c>
+      <c r="E59" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="F59" s="9" t="n"/>
+      <c r="H59" s="5" t="n">
+        <v>46188</v>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Aye Su</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="L59" t="n">
+        <v>697</v>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>2026-06-19 14:23:24</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="6" t="n"/>
-      <c r="D60" s="9" t="n"/>
-      <c r="E60" s="9" t="n"/>
+      <c r="A60" s="6" t="n">
+        <v>61</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Sote Phwar 1 L</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D60" s="9" t="n">
+        <v>33000000</v>
+      </c>
+      <c r="E60" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="F60" s="9" t="n"/>
+      <c r="H60" s="5" t="n">
+        <v>46189</v>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Ko Aung Aung</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="L60" t="n">
+        <v>698</v>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>2026-06-19 14:23:24</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="6" t="n"/>
-      <c r="D61" s="9" t="n"/>
-      <c r="E61" s="9" t="n"/>
+      <c r="A61" s="6" t="n">
+        <v>61</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Sote Phwar 500 mL</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D61" s="9" t="n">
+        <v>34000000</v>
+      </c>
+      <c r="E61" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="F61" s="9" t="n"/>
+      <c r="H61" s="5" t="n">
+        <v>46189</v>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Ko Aung Aung</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="L61" t="n">
+        <v>699</v>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>2026-06-19 14:23:24</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="6" t="n"/>
-      <c r="D62" s="9" t="n"/>
-      <c r="E62" s="9" t="n"/>
+      <c r="A62" s="6" t="n">
+        <v>62</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Sote Phwar 500 mL</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>100</v>
+      </c>
+      <c r="D62" s="9" t="n">
+        <v>1700000</v>
+      </c>
+      <c r="E62" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="F62" s="9" t="n"/>
+      <c r="H62" s="5" t="n">
+        <v>46189</v>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Aungthapyay</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="L62" t="n">
+        <v>700</v>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>2026-06-19 14:23:24</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="6" t="n"/>
-      <c r="D63" s="9" t="n"/>
-      <c r="E63" s="9" t="n"/>
+      <c r="A63" s="6" t="n">
+        <v>63</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Sote Phwar 1 L</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>500</v>
+      </c>
+      <c r="D63" s="9" t="n">
+        <v>15000000</v>
+      </c>
+      <c r="E63" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="F63" s="9" t="n"/>
+      <c r="H63" s="5" t="n">
+        <v>46189</v>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Pwint Aung Kyaw POL</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="L63" t="n">
+        <v>701</v>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>2026-06-19 14:23:24</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="6" t="n"/>
-      <c r="D64" s="9" t="n"/>
-      <c r="E64" s="9" t="n"/>
+      <c r="A64" s="6" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Sote Phwar 500 mL</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>200</v>
+      </c>
+      <c r="D64" s="9" t="n">
+        <v>3400000</v>
+      </c>
+      <c r="E64" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="F64" s="9" t="n"/>
+      <c r="H64" s="5" t="n">
+        <v>46189</v>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Pwint Aung Kyaw POL</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="L64" t="n">
+        <v>702</v>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>2026-06-19 14:23:24</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="6" t="n"/>
-      <c r="D65" s="9" t="n"/>
-      <c r="E65" s="9" t="n"/>
+      <c r="A65" s="6" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Sote Phwar 1 L</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>1100</v>
+      </c>
+      <c r="D65" s="9" t="n">
+        <v>33000000</v>
+      </c>
+      <c r="E65" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="F65" s="9" t="n"/>
+      <c r="H65" s="5" t="n">
+        <v>46189</v>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Shwe War</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="L65" t="n">
+        <v>703</v>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>2026-06-19 14:23:24</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="6" t="n"/>
-      <c r="D66" s="9" t="n"/>
-      <c r="E66" s="9" t="n"/>
+      <c r="A66" s="6" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Sote Phwar 1 L</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>100</v>
+      </c>
+      <c r="D66" s="9" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="E66" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="F66" s="9" t="n"/>
+      <c r="H66" s="5" t="n">
+        <v>46189</v>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Moe Myint Min(PW)</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="L66" t="n">
+        <v>704</v>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>2026-06-19 14:23:24</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="6" t="n"/>
-      <c r="D67" s="9" t="n"/>
-      <c r="E67" s="9" t="n"/>
+      <c r="A67" s="6" t="n">
+        <v>65</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Sote Phwar 500 mL</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>20</v>
+      </c>
+      <c r="D67" s="9" t="n">
+        <v>340000</v>
+      </c>
+      <c r="E67" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="F67" s="9" t="n"/>
+      <c r="H67" s="5" t="n">
+        <v>46189</v>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Moe Myint Min(PW)</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="L67" t="n">
+        <v>705</v>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>2026-06-19 14:23:24</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="6" t="n"/>
-      <c r="D68" s="9" t="n"/>
-      <c r="E68" s="9" t="n"/>
+      <c r="A68" s="6" t="n">
+        <v>66</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Sote Phwar 1 L</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>210</v>
+      </c>
+      <c r="D68" s="9" t="n">
+        <v>6600000</v>
+      </c>
+      <c r="E68" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="F68" s="9" t="n"/>
+      <c r="H68" s="5" t="n">
+        <v>46189</v>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Aung Kyaw Swe</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="L68" t="n">
+        <v>706</v>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>2026-06-19 14:23:24</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="6" t="n"/>
-      <c r="D69" s="9" t="n"/>
-      <c r="E69" s="9" t="n"/>
+      <c r="A69" s="6" t="n">
+        <v>66</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Sote Phwar 4L</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>4</v>
+      </c>
+      <c r="D69" s="9" t="n">
+        <v>500000</v>
+      </c>
+      <c r="E69" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="F69" s="9" t="n"/>
+      <c r="H69" s="5" t="n">
+        <v>46189</v>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Aung Kyaw Swe</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="L69" t="n">
+        <v>707</v>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>2026-06-19 14:23:24</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="6" t="n"/>
-      <c r="D70" s="9" t="n"/>
-      <c r="E70" s="9" t="n"/>
+      <c r="A70" s="6" t="n">
+        <v>67</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Sote Phwar 1 L</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>50</v>
+      </c>
+      <c r="D70" s="9" t="n">
+        <v>1650000</v>
+      </c>
+      <c r="E70" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="F70" s="9" t="n"/>
+      <c r="H70" s="5" t="n">
+        <v>46189</v>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Phyo Thein Kywal</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="L70" t="n">
+        <v>708</v>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>2026-06-19 14:23:24</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="6" t="n"/>
-      <c r="D71" s="9" t="n"/>
-      <c r="E71" s="9" t="n"/>
+      <c r="A71" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Sote Phwar 1 L</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>100</v>
+      </c>
+      <c r="D71" s="9" t="n">
+        <v>3300000</v>
+      </c>
+      <c r="E71" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="F71" s="9" t="n"/>
+      <c r="H71" s="5" t="n">
+        <v>46189</v>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Da Na Phyo Kywal</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="L71" t="n">
+        <v>709</v>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>2026-06-19 14:23:24</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="6" t="n"/>
-      <c r="D72" s="9" t="n"/>
-      <c r="E72" s="9" t="n"/>
+      <c r="A72" s="6" t="n">
+        <v>69</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Sote Phwar 1 L</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>150</v>
+      </c>
+      <c r="D72" s="9" t="n">
+        <v>4500000</v>
+      </c>
+      <c r="E72" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="F72" s="9" t="n"/>
+      <c r="H72" s="5" t="n">
+        <v>46189</v>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Pwint Aung Kyaw</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="L72" t="n">
+        <v>710</v>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>2026-06-19 14:23:24</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="6" t="n"/>
-      <c r="D73" s="9" t="n"/>
-      <c r="E73" s="9" t="n"/>
+      <c r="A73" s="6" t="n">
+        <v>69</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Sote Phwar 4L</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>8</v>
+      </c>
+      <c r="D73" s="9" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="E73" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="F73" s="9" t="n"/>
+      <c r="H73" s="5" t="n">
+        <v>46189</v>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Pwint Aung Kyaw</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="L73" t="n">
+        <v>711</v>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>2026-06-19 14:23:24</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="6" t="n"/>
-      <c r="D74" s="9" t="n"/>
-      <c r="E74" s="9" t="n"/>
+      <c r="A74" s="6" t="n">
+        <v>70</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Sote Phwar 1 L</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D74" s="9" t="n">
+        <v>33000000</v>
+      </c>
+      <c r="E74" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="F74" s="9" t="n"/>
+      <c r="H74" s="5" t="n">
+        <v>46190</v>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Myat Nyi Aung</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="L74" t="n">
+        <v>712</v>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>2026-06-19 14:23:24</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="6" t="n"/>
-      <c r="D75" s="9" t="n"/>
-      <c r="E75" s="9" t="n"/>
+      <c r="A75" s="6" t="n">
+        <v>71</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Sote Phwar 1 L</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>40</v>
+      </c>
+      <c r="D75" s="9" t="n">
+        <v>1320000</v>
+      </c>
+      <c r="E75" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="F75" s="9" t="n"/>
+      <c r="H75" s="5" t="n">
+        <v>46190</v>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Ya Way Chit Oo</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="L75" t="n">
+        <v>713</v>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>2026-06-19 14:23:24</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="6" t="n"/>
-      <c r="D76" s="9" t="n"/>
-      <c r="E76" s="9" t="n"/>
+      <c r="A76" s="6" t="n">
+        <v>71</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Sote Phwar 500 mL</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>20</v>
+      </c>
+      <c r="D76" s="9" t="n">
+        <v>340000</v>
+      </c>
+      <c r="E76" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="F76" s="9" t="n"/>
+      <c r="H76" s="5" t="n">
+        <v>46190</v>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Ya Way Chit Oo</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="L76" t="n">
+        <v>714</v>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>2026-06-19 14:23:24</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="6" t="n"/>
-      <c r="D77" s="9" t="n"/>
-      <c r="E77" s="9" t="n"/>
+      <c r="A77" s="6" t="n">
+        <v>72</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Sote Phwar 1 L</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>210</v>
+      </c>
+      <c r="D77" s="9" t="n">
+        <v>6600000</v>
+      </c>
+      <c r="E77" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="F77" s="9" t="n"/>
+      <c r="H77" s="5" t="n">
+        <v>46190</v>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Aung Kyaw Hein</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="L77" t="n">
+        <v>715</v>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>2026-06-19 14:23:24</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="6" t="n"/>
-      <c r="D78" s="9" t="n"/>
-      <c r="E78" s="9" t="n"/>
+      <c r="A78" s="6" t="n">
+        <v>73</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Sote Phwar 500 mL</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>100</v>
+      </c>
+      <c r="D78" s="9" t="n">
+        <v>1700000</v>
+      </c>
+      <c r="E78" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="F78" s="9" t="n"/>
+      <c r="H78" s="5" t="n">
+        <v>46190</v>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Theint Theint Thu</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="L78" t="n">
+        <v>716</v>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>2026-06-19 14:23:24</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="6" t="n"/>
-      <c r="D79" s="9" t="n"/>
-      <c r="E79" s="9" t="n"/>
+      <c r="A79" s="6" t="n">
+        <v>74</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Sote Phwar 1 L</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>30</v>
+      </c>
+      <c r="D79" s="9" t="n">
+        <v>990000</v>
+      </c>
+      <c r="E79" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="F79" s="9" t="n"/>
+      <c r="H79" s="5" t="n">
+        <v>46190</v>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Hein Zaw Phyo</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="L79" t="n">
+        <v>717</v>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>2026-06-19 14:23:24</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" s="6" t="n"/>
-      <c r="D80" s="9" t="n"/>
-      <c r="E80" s="9" t="n"/>
+      <c r="A80" s="6" t="n">
+        <v>75</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Sote Phwar 1 L</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>30</v>
+      </c>
+      <c r="D80" s="9" t="n">
+        <v>990000</v>
+      </c>
+      <c r="E80" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="F80" s="9" t="n"/>
+      <c r="H80" s="5" t="n">
+        <v>46190</v>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Da Na Phyo Kywal</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="L80" t="n">
+        <v>718</v>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>2026-06-19 14:23:24</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" s="6" t="n"/>
-      <c r="D81" s="9" t="n"/>
-      <c r="E81" s="9" t="n"/>
+      <c r="A81" s="6" t="n">
+        <v>76</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Sote Phwar 1 L</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>10</v>
+      </c>
+      <c r="D81" s="9" t="n">
+        <v>330000</v>
+      </c>
+      <c r="E81" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="F81" s="9" t="n"/>
+      <c r="H81" s="5" t="n">
+        <v>46190</v>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Hein Zaw Phyo</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="L81" t="n">
+        <v>719</v>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>2026-06-19 14:23:24</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" s="6" t="n"/>
-      <c r="D82" s="9" t="n"/>
-      <c r="E82" s="9" t="n"/>
+      <c r="A82" s="6" t="n">
+        <v>76</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Sote Phwar 4L</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>4</v>
+      </c>
+      <c r="D82" s="9" t="n">
+        <v>500000</v>
+      </c>
+      <c r="E82" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="F82" s="9" t="n"/>
+      <c r="H82" s="5" t="n">
+        <v>46190</v>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Hein Zaw Phyo</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="L82" t="n">
+        <v>720</v>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>2026-06-19 14:23:24</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" s="6" t="n"/>
-      <c r="D83" s="9" t="n"/>
-      <c r="E83" s="9" t="n"/>
-      <c r="F83" s="9" t="n"/>
+      <c r="A83" s="6" t="n">
+        <v>77</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Sote Phwar 1 L</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>105</v>
+      </c>
+      <c r="D83" s="9" t="n">
+        <v>3300000</v>
+      </c>
+      <c r="E83" s="9" t="n">
+        <v>3300000</v>
+      </c>
+      <c r="F83" s="9" t="inlineStr">
+        <is>
+          <t>18.6.2026 Paid Kpay MM</t>
+        </is>
+      </c>
+      <c r="H83" s="5" t="n">
+        <v>46191</v>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Thee Pwint San</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="L83" t="n">
+        <v>721</v>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>2026-06-19 14:23:24</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" s="6" t="n"/>
-      <c r="D84" s="9" t="n"/>
-      <c r="E84" s="9" t="n"/>
+      <c r="A84" s="6" t="n">
+        <v>78</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Sote Phwar 1 L</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>110</v>
+      </c>
+      <c r="D84" s="9" t="n">
+        <v>3135000</v>
+      </c>
+      <c r="E84" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="F84" s="9" t="n"/>
+      <c r="H84" s="5" t="n">
+        <v>46191</v>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Zun Ei Khaing</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="L84" t="n">
+        <v>722</v>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>2026-06-19 14:23:24</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="6" t="n"/>
-      <c r="D85" s="9" t="n"/>
-      <c r="E85" s="9" t="n"/>
+      <c r="A85" s="6" t="n">
+        <v>79</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Sote Phwar 1 L</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>100</v>
+      </c>
+      <c r="D85" s="9" t="n">
+        <v>3300000</v>
+      </c>
+      <c r="E85" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="F85" s="9" t="n"/>
+      <c r="H85" s="5" t="n">
+        <v>46191</v>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Billion</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="L85" t="n">
+        <v>723</v>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>2026-06-19 14:23:24</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" s="6" t="n"/>
-      <c r="D86" s="9" t="n"/>
-      <c r="E86" s="9" t="n"/>
+      <c r="A86" s="6" t="n">
+        <v>80</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Sote Phwar 1 L</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>210</v>
+      </c>
+      <c r="D86" s="9" t="n">
+        <v>6600000</v>
+      </c>
+      <c r="E86" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="F86" s="9" t="n"/>
+      <c r="H86" s="5" t="n">
+        <v>46192</v>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Kaung Kin Pyar</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="L86" t="n">
+        <v>724</v>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>2026-06-19 14:23:24</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" s="6" t="n"/>
-      <c r="D87" s="9" t="n"/>
-      <c r="E87" s="9" t="n"/>
+      <c r="A87" s="6" t="n">
+        <v>81</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Sote Phwar 500 mL</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>100</v>
+      </c>
+      <c r="D87" s="9" t="n">
+        <v>1700000</v>
+      </c>
+      <c r="E87" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="F87" s="9" t="n"/>
+      <c r="H87" s="5" t="n">
+        <v>46192</v>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Cetena</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="L87" t="n">
+        <v>725</v>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>2026-06-19 14:23:24</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" s="6" t="n"/>
-      <c r="D88" s="9" t="n"/>
-      <c r="E88" s="9" t="n"/>
+      <c r="A88" s="6" t="n">
+        <v>82</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Sote Phwar 1 L</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>20</v>
+      </c>
+      <c r="D88" s="9" t="n">
+        <v>660000</v>
+      </c>
+      <c r="E88" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="F88" s="9" t="n"/>
+      <c r="H88" s="5" t="n">
+        <v>46192</v>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Myat Bone Saung</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="L88" t="n">
+        <v>726</v>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>2026-06-19 14:23:24</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="6" t="n"/>

--- a/excel_import/business_data_import_template.xlsx
+++ b/excel_import/business_data_import_template.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="4420" yWindow="1200" windowWidth="25820" windowHeight="19260" tabRatio="600" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="60" yWindow="620" windowWidth="25820" windowHeight="19260" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
@@ -14,7 +14,7 @@
     <sheet name="Sotephwar_Inventory" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -149,6 +149,9 @@
       <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
+    </dxf>
+    <dxf>
       <font>
         <name val="Calibri"/>
         <family val="2"/>
@@ -198,9 +201,6 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="164" formatCode="#000000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -279,7 +279,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TransectionImport" displayName="TransectionImport" ref="A1:M389" headerRowCount="1">
   <autoFilter ref="A1:M389"/>
   <tableColumns count="13">
-    <tableColumn id="1" name="Date" dataDxfId="5"/>
+    <tableColumn id="1" name="Date" dataDxfId="0"/>
     <tableColumn id="2" name="Income_Expense"/>
     <tableColumn id="3" name="Categorization"/>
     <tableColumn id="4" name="Sector"/>
@@ -321,14 +321,14 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="SotephwarTransectionImport" displayName="SotephwarTransectionImport" ref="A1:N446" headerRowCount="1">
   <autoFilter ref="A1:N446"/>
   <tableColumns count="14">
-    <tableColumn id="1" name="Invoice_Number" dataDxfId="4"/>
+    <tableColumn id="1" name="Invoice_Number" dataDxfId="5"/>
     <tableColumn id="2" name="Item"/>
     <tableColumn id="3" name="Quantity"/>
-    <tableColumn id="4" name="Total_Amount" dataDxfId="3" dataCellStyle="Comma"/>
-    <tableColumn id="5" name="Amount_Received" dataDxfId="2" dataCellStyle="Comma"/>
-    <tableColumn id="6" name="Note" dataDxfId="1" dataCellStyle="Comma"/>
+    <tableColumn id="4" name="Total_Amount" dataDxfId="4" dataCellStyle="Comma"/>
+    <tableColumn id="5" name="Amount_Received" dataDxfId="3" dataCellStyle="Comma"/>
+    <tableColumn id="6" name="Note" dataDxfId="2" dataCellStyle="Comma"/>
     <tableColumn id="7" name="AI_comment"/>
-    <tableColumn id="8" name="Invoice_Date" dataDxfId="0"/>
+    <tableColumn id="8" name="Invoice_Date" dataDxfId="1"/>
     <tableColumn id="9" name="Customer_Name"/>
     <tableColumn id="10" name="Attachment"/>
     <tableColumn id="11" name="Upload_Status"/>
@@ -5832,698 +5832,4091 @@
       </c>
     </row>
     <row r="111" ht="26" customHeight="1">
-      <c r="A111" s="16" t="n"/>
-      <c r="B111" s="3" t="n"/>
-      <c r="C111" s="3" t="n"/>
-      <c r="E111" s="4" t="n"/>
-      <c r="F111" s="3" t="n"/>
-      <c r="G111" s="3" t="n"/>
+      <c r="A111" s="12" t="n">
+        <v>46193</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Sales incomes from others</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Farm</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>မငယ်ထံမှရငွေ</t>
+        </is>
+      </c>
+      <c r="F111" t="n">
+        <v>1030000</v>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>In Cash</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="K111" t="n">
+        <v>1746</v>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:01:31</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr"/>
     </row>
     <row r="112" ht="26" customHeight="1">
-      <c r="A112" s="16" t="n"/>
-      <c r="B112" s="3" t="n"/>
-      <c r="C112" s="3" t="n"/>
-      <c r="E112" s="3" t="n"/>
-      <c r="F112" s="3" t="n"/>
-      <c r="G112" s="3" t="n"/>
+      <c r="A112" s="12" t="n">
+        <v>46180</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Sales incomes from others</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Farm</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>မနေခြည်ဝင်းထံမှရငွေ</t>
+        </is>
+      </c>
+      <c r="F112" t="n">
+        <v>430000</v>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>In Cash</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="K112" t="n">
+        <v>1747</v>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:01:31</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr"/>
     </row>
     <row r="113" ht="26" customHeight="1">
-      <c r="A113" s="16" t="n"/>
-      <c r="B113" s="3" t="n"/>
-      <c r="C113" s="3" t="n"/>
-      <c r="E113" s="3" t="n"/>
-      <c r="F113" s="3" t="n"/>
-      <c r="G113" s="3" t="n"/>
+      <c r="A113" s="12" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Sales incomes from others</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Farm</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>On The Go ထံမှရငွေ</t>
+        </is>
+      </c>
+      <c r="F113" t="n">
+        <v>40000</v>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>In Cash</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="K113" t="n">
+        <v>1748</v>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:01:31</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr"/>
     </row>
     <row r="114" ht="26" customHeight="1">
-      <c r="A114" s="16" t="n"/>
-      <c r="B114" s="3" t="n"/>
-      <c r="C114" s="3" t="n"/>
-      <c r="E114" s="4" t="n"/>
-      <c r="F114" s="3" t="n"/>
-      <c r="G114" s="3" t="n"/>
+      <c r="A114" s="12" t="n">
+        <v>46175</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Sales incomes from others</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Farm</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Kokkoya ထံမှရငွေ</t>
+        </is>
+      </c>
+      <c r="F114" t="n">
+        <v>220000</v>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>In Cash</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="K114" t="n">
+        <v>1749</v>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:01:31</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr"/>
     </row>
     <row r="115" ht="26" customHeight="1">
-      <c r="A115" s="16" t="n"/>
-      <c r="B115" s="3" t="n"/>
-      <c r="C115" s="3" t="n"/>
-      <c r="E115" s="3" t="n"/>
-      <c r="F115" s="3" t="n"/>
-      <c r="G115" s="3" t="n"/>
+      <c r="A115" s="12" t="n">
+        <v>46177</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Sales incomes from others</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Farm</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Kokkoya ထံမှရငွေ</t>
+        </is>
+      </c>
+      <c r="F115" t="n">
+        <v>867000</v>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>In Cash</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="K115" t="n">
+        <v>1750</v>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:01:31</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr"/>
     </row>
     <row r="116" ht="26" customHeight="1">
-      <c r="A116" s="16" t="n"/>
-      <c r="B116" s="3" t="n"/>
-      <c r="C116" s="3" t="n"/>
-      <c r="E116" s="4" t="n"/>
-      <c r="F116" s="3" t="n"/>
-      <c r="G116" s="3" t="n"/>
+      <c r="A116" s="12" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Sales incomes from others</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Farm</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>မငယ်ထံမှရငွေ</t>
+        </is>
+      </c>
+      <c r="F116" t="n">
+        <v>144000</v>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>In Cash</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="K116" t="n">
+        <v>1751</v>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:01:31</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr"/>
     </row>
     <row r="117" ht="26" customHeight="1">
-      <c r="A117" s="16" t="n"/>
-      <c r="B117" s="3" t="n"/>
-      <c r="C117" s="3" t="n"/>
-      <c r="E117" s="3" t="n"/>
-      <c r="F117" s="3" t="n"/>
-      <c r="G117" s="3" t="n"/>
+      <c r="A117" s="12" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Sales incomes from others</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Farm</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>မငယ်ထံမှရငွေ</t>
+        </is>
+      </c>
+      <c r="F117" t="n">
+        <v>126000</v>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>In Cash</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="K117" t="n">
+        <v>1752</v>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:01:31</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr"/>
     </row>
     <row r="118" ht="26" customHeight="1">
-      <c r="A118" s="16" t="n"/>
-      <c r="B118" s="3" t="n"/>
-      <c r="C118" s="3" t="n"/>
-      <c r="E118" s="3" t="n"/>
-      <c r="F118" s="3" t="n"/>
-      <c r="G118" s="3" t="n"/>
+      <c r="A118" s="12" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Sales incomes from others</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Farm</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>KKထံမှရငွေ</t>
+        </is>
+      </c>
+      <c r="F118" t="n">
+        <v>1108000</v>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>In Cash</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="K118" t="n">
+        <v>1753</v>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:01:31</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr"/>
     </row>
     <row r="119" ht="26" customHeight="1">
-      <c r="A119" s="16" t="n"/>
-      <c r="B119" s="3" t="n"/>
-      <c r="C119" s="3" t="n"/>
-      <c r="E119" s="4" t="n"/>
-      <c r="F119" s="3" t="n"/>
-      <c r="G119" s="3" t="n"/>
+      <c r="A119" s="12" t="n">
+        <v>46177</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Sales incomes from others</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Farm</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>မယဉ်ယဉ်အေးထံမှရငွေ</t>
+        </is>
+      </c>
+      <c r="F119" t="n">
+        <v>4721000</v>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>In Cash</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="K119" t="n">
+        <v>1754</v>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:01:31</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr"/>
     </row>
     <row r="120" ht="26" customHeight="1">
-      <c r="A120" s="16" t="n"/>
-      <c r="B120" s="3" t="n"/>
-      <c r="C120" s="3" t="n"/>
-      <c r="E120" s="4" t="n"/>
-      <c r="F120" s="3" t="n"/>
-      <c r="G120" s="3" t="n"/>
+      <c r="A120" s="12" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Sales incomes from others</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Farm</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>မွန်လေးထံမှရငွေ</t>
+        </is>
+      </c>
+      <c r="F120" t="n">
+        <v>1056000</v>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>In Cash</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="K120" t="n">
+        <v>1755</v>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:01:31</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr"/>
     </row>
     <row r="121" ht="26" customHeight="1">
-      <c r="A121" s="16" t="n"/>
-      <c r="B121" s="3" t="n"/>
-      <c r="C121" s="3" t="n"/>
-      <c r="E121" s="3" t="n"/>
-      <c r="F121" s="3" t="n"/>
-      <c r="G121" s="3" t="n"/>
+      <c r="A121" s="12" t="n">
+        <v>46177</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Sales incomes from others</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Farm</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Kokkoya ထံမှရငွေ</t>
+        </is>
+      </c>
+      <c r="F121" t="n">
+        <v>867000</v>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>In Cash</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="K121" t="n">
+        <v>1756</v>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:01:31</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr"/>
     </row>
     <row r="122" ht="26" customHeight="1">
-      <c r="A122" s="16" t="n"/>
-      <c r="B122" s="3" t="n"/>
-      <c r="C122" s="3" t="n"/>
-      <c r="E122" s="3" t="n"/>
-      <c r="F122" s="3" t="n"/>
-      <c r="G122" s="3" t="n"/>
+      <c r="A122" s="12" t="n">
+        <v>46175</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Sales incomes from others</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Farm</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Kokkoya ထံမှရငွေ</t>
+        </is>
+      </c>
+      <c r="F122" t="n">
+        <v>515000</v>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>In Cash</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="K122" t="n">
+        <v>1757</v>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:01:31</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr"/>
     </row>
     <row r="123" ht="26" customHeight="1">
-      <c r="A123" s="16" t="n"/>
-      <c r="B123" s="3" t="n"/>
-      <c r="C123" s="3" t="n"/>
-      <c r="E123" s="4" t="n"/>
-      <c r="F123" s="3" t="n"/>
-      <c r="G123" s="3" t="n"/>
+      <c r="A123" s="12" t="n">
+        <v>46192</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Sales incomes from others</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Farm</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>ကိုဖုန်းထံမှရငွေ</t>
+        </is>
+      </c>
+      <c r="F123" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>In Cash</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="K123" t="n">
+        <v>1758</v>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:01:31</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr"/>
     </row>
     <row r="124" ht="26" customHeight="1">
-      <c r="A124" s="16" t="n"/>
-      <c r="B124" s="3" t="n"/>
-      <c r="C124" s="3" t="n"/>
-      <c r="E124" s="4" t="n"/>
-      <c r="F124" s="3" t="n"/>
-      <c r="G124" s="3" t="n"/>
+      <c r="A124" s="12" t="n">
+        <v>46193</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Agrochemical Income</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Farm</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>ပီတိဝေမှရငွေ</t>
+        </is>
+      </c>
+      <c r="F124" t="n">
+        <v>1316520</v>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>In Cash</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="K124" t="n">
+        <v>1759</v>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:01:31</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr"/>
     </row>
     <row r="125" ht="26" customHeight="1">
-      <c r="A125" s="16" t="n"/>
-      <c r="B125" s="3" t="n"/>
-      <c r="C125" s="3" t="n"/>
-      <c r="E125" s="3" t="n"/>
-      <c r="F125" s="3" t="n"/>
-      <c r="G125" s="3" t="n"/>
+      <c r="A125" s="12" t="n">
+        <v>46194</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Makro Expense</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Farm</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>သကြားပြောင်း၊ရှမ်းပြောင်း</t>
+        </is>
+      </c>
+      <c r="F125" t="n">
+        <v>330000</v>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>In Cash</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="K125" t="n">
+        <v>1760</v>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:01:31</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr"/>
     </row>
     <row r="126" ht="26" customHeight="1">
-      <c r="A126" s="16" t="n"/>
-      <c r="B126" s="3" t="n"/>
-      <c r="C126" s="3" t="n"/>
-      <c r="E126" s="3" t="n"/>
-      <c r="F126" s="3" t="n"/>
-      <c r="G126" s="3" t="n"/>
+      <c r="A126" s="12" t="n">
+        <v>46193</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Makro Expense</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Farm</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Makro အော်ဒါအတွက် ဂေါ်ဖီခင်းဝယ် စရံပေး</t>
+        </is>
+      </c>
+      <c r="F126" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>In Cash</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="K126" t="n">
+        <v>1761</v>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:01:31</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr"/>
     </row>
     <row r="127" ht="26" customHeight="1">
-      <c r="A127" s="16" t="n"/>
-      <c r="B127" s="3" t="n"/>
-      <c r="C127" s="3" t="n"/>
-      <c r="E127" s="3" t="n"/>
-      <c r="F127" s="3" t="n"/>
-      <c r="G127" s="3" t="n"/>
+      <c r="A127" s="12" t="n">
+        <v>46194</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Machinery equipment and maintenance</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Farm</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Sonalika (နောဇယ်22276)ပြုပြင်</t>
+        </is>
+      </c>
+      <c r="F127" t="n">
+        <v>750000</v>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>In Cash</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="K127" t="n">
+        <v>1762</v>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:01:31</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr"/>
     </row>
     <row r="128" ht="26" customHeight="1">
-      <c r="A128" s="16" t="n"/>
-      <c r="B128" s="3" t="n"/>
-      <c r="C128" s="3" t="n"/>
-      <c r="E128" s="4" t="n"/>
-      <c r="F128" s="3" t="n"/>
-      <c r="G128" s="3" t="n"/>
+      <c r="A128" s="12" t="n">
+        <v>46194</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Makro Expense</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Farm</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>ဂျပ်ဖာပို့ကားခ</t>
+        </is>
+      </c>
+      <c r="F128" t="n">
+        <v>42000</v>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>In Cash</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="K128" t="n">
+        <v>1763</v>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:01:31</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr"/>
     </row>
     <row r="129" ht="26" customHeight="1">
-      <c r="A129" s="16" t="n"/>
-      <c r="B129" s="3" t="n"/>
-      <c r="C129" s="3" t="n"/>
-      <c r="E129" s="4" t="n"/>
-      <c r="F129" s="3" t="n"/>
-      <c r="G129" s="3" t="n"/>
+      <c r="A129" s="12" t="n">
+        <v>46193</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Cultivation requirement</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Farm</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>ဖွဲပြာတိုက်</t>
+        </is>
+      </c>
+      <c r="F129" t="n">
+        <v>20000</v>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>In Cash</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="K129" t="n">
+        <v>1764</v>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:01:31</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr"/>
     </row>
     <row r="130" ht="26" customHeight="1">
-      <c r="A130" s="16" t="n"/>
-      <c r="B130" s="3" t="n"/>
-      <c r="C130" s="3" t="n"/>
-      <c r="E130" s="4" t="n"/>
-      <c r="F130" s="3" t="n"/>
-      <c r="G130" s="3" t="n"/>
+      <c r="A130" s="12" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Plumbing accessories</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Farm</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>ဆီလီကွန်၊ဆီလီဂန်း</t>
+        </is>
+      </c>
+      <c r="F130" t="n">
+        <v>111000</v>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>In Cash</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="K130" t="n">
+        <v>1765</v>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:01:31</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr"/>
     </row>
     <row r="131" ht="26" customHeight="1">
-      <c r="A131" s="16" t="n"/>
-      <c r="B131" s="3" t="n"/>
-      <c r="C131" s="3" t="n"/>
-      <c r="E131" s="3" t="n"/>
-      <c r="F131" s="3" t="n"/>
-      <c r="G131" s="3" t="n"/>
+      <c r="A131" s="12" t="n">
+        <v>46192</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>General Expense</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Farm</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>ဖော့တုံး၊အမှိုက်ပစ်</t>
+        </is>
+      </c>
+      <c r="F131" t="n">
+        <v>12000</v>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>In Cash</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="K131" t="n">
+        <v>1766</v>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:01:31</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr"/>
     </row>
     <row r="132" ht="26" customHeight="1">
-      <c r="A132" s="16" t="n"/>
-      <c r="B132" s="3" t="n"/>
-      <c r="C132" s="3" t="n"/>
-      <c r="E132" s="4" t="n"/>
-      <c r="F132" s="3" t="n"/>
-      <c r="G132" s="3" t="n"/>
+      <c r="A132" s="12" t="n">
+        <v>46192</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Machinery equipment and maintenance</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Farm</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>ဘီးဖာ‌၊လေချိန်၊လေစစ်မှုတ်</t>
+        </is>
+      </c>
+      <c r="F132" t="n">
+        <v>10000</v>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>In Cash</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="K132" t="n">
+        <v>1767</v>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:01:31</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr"/>
     </row>
     <row r="133" ht="26" customHeight="1">
-      <c r="A133" s="16" t="n"/>
-      <c r="B133" s="3" t="n"/>
-      <c r="C133" s="3" t="n"/>
-      <c r="E133" s="3" t="n"/>
-      <c r="F133" s="3" t="n"/>
-      <c r="G133" s="3" t="n"/>
+      <c r="A133" s="12" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>General Expense</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Farm</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>20 Liter ရေသန့်ဘူး(18)ဘူးလဲ</t>
+        </is>
+      </c>
+      <c r="F133" t="n">
+        <v>18000</v>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>In Cash</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="K133" t="n">
+        <v>1768</v>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:01:31</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr"/>
     </row>
     <row r="134" ht="26" customHeight="1">
-      <c r="A134" s="16" t="n"/>
-      <c r="B134" s="3" t="n"/>
-      <c r="C134" s="3" t="n"/>
-      <c r="E134" s="3" t="n"/>
-      <c r="F134" s="3" t="n"/>
-      <c r="G134" s="3" t="n"/>
+      <c r="A134" s="12" t="n">
+        <v>46189</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Fuel (Diesel)</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Farm</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Premium Diesel(4N/4732)</t>
+        </is>
+      </c>
+      <c r="F134" t="n">
+        <v>430000</v>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>In Cash</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="K134" t="n">
+        <v>1769</v>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:01:31</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr"/>
     </row>
     <row r="135" ht="26" customHeight="1">
-      <c r="A135" s="16" t="n"/>
-      <c r="B135" s="3" t="n"/>
-      <c r="C135" s="3" t="n"/>
-      <c r="E135" s="4" t="n"/>
-      <c r="F135" s="3" t="n"/>
-      <c r="G135" s="3" t="n"/>
+      <c r="A135" s="12" t="n">
+        <v>46192</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Machinery equipment and maintenance</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Farm</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>4N/4732) ဘရိတ်ရှူး၊ဘရိတ်ဆီ၊ ပြုပြင်လက်ခ</t>
+        </is>
+      </c>
+      <c r="F135" t="n">
+        <v>145000</v>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>In Cash</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="K135" t="n">
+        <v>1770</v>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:01:31</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr"/>
     </row>
     <row r="136" ht="26" customHeight="1">
-      <c r="A136" s="16" t="n"/>
-      <c r="B136" s="3" t="n"/>
-      <c r="C136" s="3" t="n"/>
-      <c r="E136" s="4" t="n"/>
-      <c r="F136" s="3" t="n"/>
-      <c r="G136" s="3" t="n"/>
+      <c r="A136" s="12" t="n">
+        <v>46184</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Machinery equipment and maintenance</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Farm</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Pump</t>
+        </is>
+      </c>
+      <c r="F136" t="n">
+        <v>244000</v>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>In Cash</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="K136" t="n">
+        <v>1771</v>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:01:31</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr"/>
     </row>
     <row r="137" ht="26" customHeight="1">
-      <c r="A137" s="16" t="n"/>
-      <c r="B137" s="3" t="n"/>
-      <c r="C137" s="3" t="n"/>
-      <c r="E137" s="3" t="n"/>
-      <c r="F137" s="3" t="n"/>
-      <c r="G137" s="3" t="n"/>
+      <c r="A137" s="12" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Machinery equipment and maintenance</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Farm</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>(4N/4732)ကားပြင်လက်ခ</t>
+        </is>
+      </c>
+      <c r="F137" t="n">
+        <v>35000</v>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>In Cash</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="K137" t="n">
+        <v>1772</v>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:01:31</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr"/>
     </row>
     <row r="138" ht="26" customHeight="1">
-      <c r="A138" s="16" t="n"/>
-      <c r="B138" s="3" t="n"/>
-      <c r="C138" s="3" t="n"/>
-      <c r="E138" s="4" t="n"/>
-      <c r="F138" s="3" t="n"/>
-      <c r="G138" s="3" t="n"/>
+      <c r="A138" s="12" t="n">
+        <v>46193</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Machinery equipment and maintenance</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Farm</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>(4A/4732)မော်တာကာဗွန်လဲ(ကားကြမ်း)</t>
+        </is>
+      </c>
+      <c r="F138" t="n">
+        <v>40000</v>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>In Cash</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="K138" t="n">
+        <v>1773</v>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:01:31</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr"/>
     </row>
     <row r="139" ht="26" customHeight="1">
-      <c r="A139" s="16" t="n"/>
-      <c r="B139" s="3" t="n"/>
-      <c r="C139" s="3" t="n"/>
-      <c r="E139" s="4" t="n"/>
-      <c r="F139" s="3" t="n"/>
-      <c r="G139" s="3" t="n"/>
+      <c r="A139" s="12" t="n">
+        <v>46192</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Agrochemical</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Farm</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>ဝိစာရသို့ဆေးဖိုးလွှဲ</t>
+        </is>
+      </c>
+      <c r="F139" t="n">
+        <v>22373590</v>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>In Cash</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="K139" t="n">
+        <v>1774</v>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:01:31</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr"/>
     </row>
     <row r="140" ht="26" customHeight="1">
-      <c r="A140" s="16" t="n"/>
-      <c r="B140" s="3" t="n"/>
-      <c r="C140" s="3" t="n"/>
-      <c r="E140" s="4" t="n"/>
-      <c r="F140" s="3" t="n"/>
-      <c r="G140" s="3" t="n"/>
+      <c r="A140" s="12" t="n">
+        <v>46192</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>GAP Expense</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Farm</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>ဧည့်သည်ထမင်းကျွေး</t>
+        </is>
+      </c>
+      <c r="F140" t="n">
+        <v>228500</v>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>In Cash</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="K140" t="n">
+        <v>1775</v>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:01:31</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr"/>
     </row>
     <row r="141" ht="26" customHeight="1">
-      <c r="A141" s="16" t="n"/>
-      <c r="B141" s="3" t="n"/>
-      <c r="C141" s="3" t="n"/>
-      <c r="E141" s="3" t="n"/>
-      <c r="F141" s="3" t="n"/>
-      <c r="G141" s="3" t="n"/>
+      <c r="A141" s="12" t="n">
+        <v>46192</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>GAP Expense</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Farm</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ဆီဖိုး </t>
+        </is>
+      </c>
+      <c r="F141" t="n">
+        <v>100000</v>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>In Cash</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="K141" t="n">
+        <v>1776</v>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:01:31</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr"/>
     </row>
     <row r="142" ht="26" customHeight="1">
-      <c r="A142" s="16" t="n"/>
-      <c r="B142" s="3" t="n"/>
-      <c r="C142" s="3" t="n"/>
-      <c r="E142" s="3" t="n"/>
-      <c r="F142" s="3" t="n"/>
-      <c r="G142" s="3" t="n"/>
+      <c r="A142" s="12" t="n">
+        <v>46192</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Electrical Cost </t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Farm</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>မီတာခ</t>
+        </is>
+      </c>
+      <c r="F142" t="n">
+        <v>331750</v>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>In Cash</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="K142" t="n">
+        <v>1777</v>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:01:31</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr"/>
     </row>
     <row r="143" ht="26" customHeight="1">
-      <c r="A143" s="16" t="n"/>
-      <c r="B143" s="3" t="n"/>
-      <c r="C143" s="3" t="n"/>
-      <c r="E143" s="3" t="n"/>
-      <c r="F143" s="3" t="n"/>
-      <c r="G143" s="3" t="n"/>
+      <c r="A143" s="12" t="n">
+        <v>46191</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Makro Expense</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Farm</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>ရှမ်းပြောင်း၊သကြားပြောင်း</t>
+        </is>
+      </c>
+      <c r="F143" t="n">
+        <v>285000</v>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>In Cash</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="K143" t="n">
+        <v>1778</v>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:01:31</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr"/>
     </row>
     <row r="144" ht="26" customHeight="1">
-      <c r="A144" s="16" t="n"/>
-      <c r="B144" s="3" t="n"/>
-      <c r="C144" s="3" t="n"/>
-      <c r="E144" s="3" t="n"/>
-      <c r="F144" s="3" t="n"/>
-      <c r="G144" s="3" t="n"/>
+      <c r="A144" s="12" t="n">
+        <v>46192</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Cultivation requirement</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Farm</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>ဖွဲပြာတိုက်</t>
+        </is>
+      </c>
+      <c r="F144" t="n">
+        <v>25000</v>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>In Cash</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="K144" t="n">
+        <v>1779</v>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:01:31</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr"/>
     </row>
     <row r="145" ht="26" customHeight="1">
-      <c r="A145" s="16" t="n"/>
-      <c r="B145" s="3" t="n"/>
-      <c r="C145" s="3" t="n"/>
-      <c r="E145" s="4" t="n"/>
-      <c r="F145" s="3" t="n"/>
-      <c r="G145" s="3" t="n"/>
+      <c r="A145" s="12" t="n">
+        <v>46192</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Machinery equipment and maintenance</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Farm</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Sonalika အင်ဂျင်ကိုင်လက်ခ</t>
+        </is>
+      </c>
+      <c r="F145" t="n">
+        <v>180000</v>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>In Cash</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="K145" t="n">
+        <v>1780</v>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:01:31</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr"/>
     </row>
     <row r="146" ht="26" customHeight="1">
-      <c r="A146" s="16" t="n"/>
-      <c r="B146" s="3" t="n"/>
-      <c r="C146" s="3" t="n"/>
-      <c r="E146" s="4" t="n"/>
-      <c r="F146" s="3" t="n"/>
-      <c r="G146" s="3" t="n"/>
+      <c r="A146" s="12" t="n">
+        <v>46191</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Machinery equipment and maintenance</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Farm</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Sonalika 100 piston</t>
+        </is>
+      </c>
+      <c r="F146" t="n">
+        <v>500000</v>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>In Cash</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="K146" t="n">
+        <v>1781</v>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:01:31</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr"/>
     </row>
     <row r="147" ht="26" customHeight="1">
-      <c r="A147" s="16" t="n"/>
-      <c r="B147" s="3" t="n"/>
-      <c r="C147" s="3" t="n"/>
-      <c r="E147" s="4" t="n"/>
-      <c r="F147" s="3" t="n"/>
-      <c r="G147" s="3" t="n"/>
+      <c r="A147" s="12" t="n">
+        <v>46191</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Makro Expense</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Farm</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>အာလူး</t>
+        </is>
+      </c>
+      <c r="F147" t="n">
+        <v>578100</v>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>In Cash</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="K147" t="n">
+        <v>1782</v>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:01:31</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr"/>
     </row>
     <row r="148" ht="26" customHeight="1">
-      <c r="A148" s="16" t="n"/>
-      <c r="B148" s="3" t="n"/>
-      <c r="C148" s="3" t="n"/>
-      <c r="E148" s="4" t="n"/>
-      <c r="F148" s="3" t="n"/>
-      <c r="G148" s="3" t="n"/>
+      <c r="A148" s="12" t="n">
+        <v>46191</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Makro Expense</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Farm</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>မုံညင်း</t>
+        </is>
+      </c>
+      <c r="F148" t="n">
+        <v>582000</v>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>In Cash</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="K148" t="n">
+        <v>1783</v>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:01:31</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr"/>
     </row>
     <row r="149" ht="26" customHeight="1">
-      <c r="A149" s="16" t="n"/>
-      <c r="B149" s="3" t="n"/>
-      <c r="C149" s="3" t="n"/>
-      <c r="E149" s="3" t="n"/>
-      <c r="F149" s="3" t="n"/>
-      <c r="G149" s="3" t="n"/>
+      <c r="A149" s="12" t="n">
+        <v>46191</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Makro Expense</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Farm</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>ပန်းပွင့်</t>
+        </is>
+      </c>
+      <c r="F149" t="n">
+        <v>445000</v>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>In Cash</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="K149" t="n">
+        <v>1784</v>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:01:31</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr"/>
     </row>
     <row r="150" ht="26" customHeight="1">
-      <c r="A150" s="16" t="n"/>
-      <c r="B150" s="3" t="n"/>
-      <c r="C150" s="3" t="n"/>
-      <c r="E150" s="4" t="n"/>
-      <c r="F150" s="3" t="n"/>
-      <c r="G150" s="3" t="n"/>
+      <c r="A150" s="12" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Fuel (Octane)</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Farm</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>အော်ဒါဆိုင်ကယ်(92)</t>
+        </is>
+      </c>
+      <c r="F150" t="n">
+        <v>12000</v>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>In Cash</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="K150" t="n">
+        <v>1785</v>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:01:31</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr"/>
     </row>
     <row r="151" ht="26" customHeight="1">
-      <c r="A151" s="16" t="n"/>
-      <c r="B151" s="3" t="n"/>
-      <c r="C151" s="3" t="n"/>
-      <c r="E151" s="4" t="n"/>
-      <c r="F151" s="3" t="n"/>
-      <c r="G151" s="3" t="n"/>
+      <c r="A151" s="12" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Makro Expense</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Farm</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>ရှမ်းပြောင်း၊သကြားပြောင်း</t>
+        </is>
+      </c>
+      <c r="F151" t="n">
+        <v>310000</v>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>In Cash</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="K151" t="n">
+        <v>1786</v>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:01:31</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr"/>
     </row>
     <row r="152" ht="26" customHeight="1">
-      <c r="A152" s="16" t="n"/>
-      <c r="B152" s="3" t="n"/>
-      <c r="C152" s="3" t="n"/>
-      <c r="E152" s="4" t="n"/>
-      <c r="F152" s="3" t="n"/>
-      <c r="G152" s="3" t="n"/>
+      <c r="A152" s="12" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Paddy Field Costs</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Farm</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>လယ်စရိတ်</t>
+        </is>
+      </c>
+      <c r="F152" t="n">
+        <v>412000</v>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>In Cash</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="K152" t="n">
+        <v>1787</v>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:01:31</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr"/>
     </row>
     <row r="153" ht="26" customHeight="1">
-      <c r="A153" s="16" t="n"/>
-      <c r="B153" s="3" t="n"/>
-      <c r="C153" s="3" t="n"/>
-      <c r="E153" s="4" t="n"/>
-      <c r="F153" s="3" t="n"/>
-      <c r="G153" s="3" t="n"/>
+      <c r="A153" s="12" t="n">
+        <v>46189</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Agrochemical</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Farm</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>ဖိနိစင်(1)လီတာ၊ဖပရို (1)kg</t>
+        </is>
+      </c>
+      <c r="F153" t="n">
+        <v>1095000</v>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>In Cash</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="K153" t="n">
+        <v>1788</v>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:01:31</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr"/>
     </row>
     <row r="154" ht="26" customHeight="1">
-      <c r="A154" s="16" t="n"/>
-      <c r="B154" s="3" t="n"/>
-      <c r="C154" s="3" t="n"/>
-      <c r="E154" s="4" t="n"/>
-      <c r="F154" s="3" t="n"/>
-      <c r="G154" s="3" t="n"/>
+      <c r="A154" s="12" t="n">
+        <v>46189</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Fuel (Octane)</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Farm</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>သုံးဘီး</t>
+        </is>
+      </c>
+      <c r="F154" t="n">
+        <v>40000</v>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>In Cash</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="K154" t="n">
+        <v>1789</v>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:01:31</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr"/>
     </row>
     <row r="155" ht="26" customHeight="1">
-      <c r="A155" s="16" t="n"/>
-      <c r="B155" s="3" t="n"/>
-      <c r="C155" s="3" t="n"/>
-      <c r="E155" s="4" t="n"/>
-      <c r="F155" s="3" t="n"/>
-      <c r="G155" s="3" t="n"/>
+      <c r="A155" s="12" t="n">
+        <v>46189</v>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Fuel (Octane)</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Farm</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>သုံးဘီး</t>
+        </is>
+      </c>
+      <c r="F155" t="n">
+        <v>74000</v>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>In Cash</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="K155" t="n">
+        <v>1790</v>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:01:31</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr"/>
     </row>
     <row r="156" ht="26" customHeight="1">
-      <c r="A156" s="16" t="n"/>
-      <c r="B156" s="3" t="n"/>
-      <c r="C156" s="3" t="n"/>
-      <c r="E156" s="3" t="n"/>
-      <c r="F156" s="3" t="n"/>
-      <c r="G156" s="3" t="n"/>
+      <c r="A156" s="12" t="n">
+        <v>46180</v>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Makro Expense</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Farm</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>မုံညင်း</t>
+        </is>
+      </c>
+      <c r="F156" t="n">
+        <v>361000</v>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>In Cash</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="K156" t="n">
+        <v>1791</v>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:01:31</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr"/>
     </row>
     <row r="157" ht="26" customHeight="1">
-      <c r="A157" s="16" t="n"/>
-      <c r="B157" s="3" t="n"/>
-      <c r="C157" s="3" t="n"/>
-      <c r="E157" s="3" t="n"/>
-      <c r="F157" s="3" t="n"/>
-      <c r="G157" s="3" t="n"/>
+      <c r="A157" s="12" t="n">
+        <v>46180</v>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Makro Expense</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Farm</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>ပန်းပွင့်</t>
+        </is>
+      </c>
+      <c r="F157" t="n">
+        <v>185500</v>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>In Cash</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="K157" t="n">
+        <v>1792</v>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:01:31</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr"/>
     </row>
     <row r="158" ht="26" customHeight="1">
-      <c r="A158" s="16" t="n"/>
-      <c r="B158" s="3" t="n"/>
-      <c r="C158" s="3" t="n"/>
-      <c r="E158" s="3" t="n"/>
-      <c r="F158" s="3" t="n"/>
-      <c r="G158" s="3" t="n"/>
+      <c r="A158" s="12" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Makro Expense</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Farm</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>မုံညင်း</t>
+        </is>
+      </c>
+      <c r="F158" t="n">
+        <v>709600</v>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>In Cash</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="K158" t="n">
+        <v>1793</v>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:01:31</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr"/>
     </row>
     <row r="159" ht="26" customHeight="1">
-      <c r="A159" s="16" t="n"/>
-      <c r="B159" s="3" t="n"/>
-      <c r="C159" s="3" t="n"/>
-      <c r="E159" s="3" t="n"/>
-      <c r="F159" s="3" t="n"/>
-      <c r="G159" s="3" t="n"/>
+      <c r="A159" s="12" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Makro Expense</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Farm</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>ပန်းပွင့်</t>
+        </is>
+      </c>
+      <c r="F159" t="n">
+        <v>22000</v>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>In Cash</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="K159" t="n">
+        <v>1794</v>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:01:31</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr"/>
     </row>
     <row r="160" ht="26" customHeight="1">
-      <c r="A160" s="16" t="n"/>
-      <c r="B160" s="3" t="n"/>
-      <c r="C160" s="3" t="n"/>
-      <c r="E160" s="4" t="n"/>
-      <c r="F160" s="3" t="n"/>
-      <c r="G160" s="3" t="n"/>
+      <c r="A160" s="12" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Makro Expense</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Farm</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>သကြားပြောင်း</t>
+        </is>
+      </c>
+      <c r="F160" t="n">
+        <v>165000</v>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>In Cash</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="K160" t="n">
+        <v>1795</v>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:01:31</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr"/>
     </row>
     <row r="161" ht="26" customHeight="1">
-      <c r="A161" s="16" t="n"/>
-      <c r="B161" s="3" t="n"/>
-      <c r="C161" s="3" t="n"/>
-      <c r="E161" s="3" t="n"/>
-      <c r="F161" s="3" t="n"/>
-      <c r="G161" s="3" t="n"/>
+      <c r="A161" s="12" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Makro Expense</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Farm</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>ပန်းပွင့်</t>
+        </is>
+      </c>
+      <c r="F161" t="n">
+        <v>235000</v>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>In Cash</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="K161" t="n">
+        <v>1796</v>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:01:31</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr"/>
     </row>
     <row r="162">
-      <c r="A162" s="16" t="n"/>
-      <c r="B162" s="3" t="n"/>
-      <c r="C162" s="3" t="n"/>
-      <c r="E162" s="3" t="n"/>
-      <c r="F162" s="3" t="n"/>
-      <c r="G162" s="3" t="n"/>
+      <c r="A162" s="12" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Makro Expense</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Farm</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>မုံညင်း</t>
+        </is>
+      </c>
+      <c r="F162" t="n">
+        <v>710400</v>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>In Cash</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="K162" t="n">
+        <v>1797</v>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:01:31</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr"/>
     </row>
     <row r="163" ht="26" customHeight="1">
-      <c r="A163" s="16" t="n"/>
-      <c r="B163" s="3" t="n"/>
-      <c r="C163" s="3" t="n"/>
-      <c r="E163" s="3" t="n"/>
-      <c r="F163" s="3" t="n"/>
-      <c r="G163" s="3" t="n"/>
+      <c r="A163" s="12" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Makro Expense</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Farm</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>သကြားပြောင်း</t>
+        </is>
+      </c>
+      <c r="F163" t="n">
+        <v>110000</v>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>In Cash</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="K163" t="n">
+        <v>1798</v>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:01:31</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr"/>
     </row>
     <row r="164" ht="26" customHeight="1">
-      <c r="A164" s="16" t="n"/>
-      <c r="B164" s="3" t="n"/>
-      <c r="C164" s="3" t="n"/>
-      <c r="E164" s="4" t="n"/>
-      <c r="F164" s="3" t="n"/>
-      <c r="G164" s="3" t="n"/>
+      <c r="A164" s="12" t="n">
+        <v>46193</v>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Carriage Inward</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Sote Phwar</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>စုပ်ဖွားအင်္ကျီ ပို့ကားခ</t>
+        </is>
+      </c>
+      <c r="F164" t="n">
+        <v>44000</v>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>By Cash</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="K164" t="n">
+        <v>1799</v>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:01:31</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr"/>
     </row>
     <row r="165" ht="26" customHeight="1">
-      <c r="A165" s="16" t="n"/>
-      <c r="B165" s="3" t="n"/>
-      <c r="C165" s="3" t="n"/>
-      <c r="E165" s="3" t="n"/>
-      <c r="F165" s="3" t="n"/>
-      <c r="G165" s="3" t="n"/>
+      <c r="A165" s="12" t="n">
+        <v>46193</v>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Machinery repair &amp; maintenance </t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Sote Phwar</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Welding Machine</t>
+        </is>
+      </c>
+      <c r="F165" t="n">
+        <v>570000</v>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>By Cash</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="K165" t="n">
+        <v>1800</v>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:01:31</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr"/>
     </row>
     <row r="166" ht="26" customHeight="1">
-      <c r="A166" s="16" t="n"/>
-      <c r="B166" s="3" t="n"/>
-      <c r="C166" s="3" t="n"/>
-      <c r="E166" s="4" t="n"/>
-      <c r="F166" s="3" t="n"/>
-      <c r="G166" s="3" t="n"/>
+      <c r="A166" s="12" t="n">
+        <v>46193</v>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Fish</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Sote Phwar</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>868.50ပိဿာ*4700(ဒေါ်ခင်ညွှန့်)</t>
+        </is>
+      </c>
+      <c r="F166" t="n">
+        <v>4081950</v>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>By Cash</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="K166" t="n">
+        <v>1801</v>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:01:31</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr"/>
     </row>
     <row r="167" ht="26" customHeight="1">
-      <c r="A167" s="16" t="n"/>
-      <c r="B167" s="3" t="n"/>
-      <c r="C167" s="3" t="n"/>
-      <c r="E167" s="4" t="n"/>
-      <c r="F167" s="3" t="n"/>
-      <c r="G167" s="3" t="n"/>
+      <c r="A167" s="12" t="n">
+        <v>46193</v>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Fish</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Sote Phwar</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>989.25ပိဿာ*4700(ဇင်ယော်)</t>
+        </is>
+      </c>
+      <c r="F167" t="n">
+        <v>4649475</v>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>By Cash</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="K167" t="n">
+        <v>1802</v>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:01:31</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr"/>
     </row>
     <row r="168" ht="26" customHeight="1">
-      <c r="A168" s="16" t="n"/>
-      <c r="B168" s="3" t="n"/>
-      <c r="C168" s="3" t="n"/>
-      <c r="E168" s="4" t="n"/>
-      <c r="F168" s="3" t="n"/>
-      <c r="G168" s="3" t="n"/>
+      <c r="A168" s="12" t="n">
+        <v>46193</v>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Warehouse Maintenance Expense</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Sote Phwar</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>3Hp  3P  မော်တာ(6P)</t>
+        </is>
+      </c>
+      <c r="F168" t="n">
+        <v>1100000</v>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>By K-Pay</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="K168" t="n">
+        <v>1803</v>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:01:31</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr"/>
     </row>
     <row r="169" ht="26" customHeight="1">
-      <c r="A169" s="16" t="n"/>
-      <c r="B169" s="3" t="n"/>
-      <c r="C169" s="3" t="n"/>
-      <c r="E169" s="3" t="n"/>
-      <c r="F169" s="3" t="n"/>
-      <c r="G169" s="3" t="n"/>
+      <c r="A169" s="12" t="n">
+        <v>46193</v>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Warehouse Maintenance Expense</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Sote Phwar</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>2G  2W</t>
+        </is>
+      </c>
+      <c r="F169" t="n">
+        <v>12000</v>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>By Cash</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="K169" t="n">
+        <v>1804</v>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:01:31</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr"/>
     </row>
     <row r="170" ht="26" customHeight="1">
-      <c r="A170" s="16" t="n"/>
-      <c r="B170" s="3" t="n"/>
-      <c r="C170" s="3" t="n"/>
-      <c r="E170" s="4" t="n"/>
-      <c r="F170" s="3" t="n"/>
-      <c r="G170" s="3" t="n"/>
+      <c r="A170" s="12" t="n">
+        <v>46192</v>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Warehouse Maintenance Expense</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Sote Phwar</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>ပလပ်၊စပန်နာ၊Air Con S.K  ၊81 Protector</t>
+        </is>
+      </c>
+      <c r="F170" t="n">
+        <v>51500</v>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>By Cash</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="K170" t="n">
+        <v>1805</v>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:01:31</t>
+        </is>
+      </c>
+      <c r="M170" t="inlineStr"/>
     </row>
     <row r="171" ht="26" customHeight="1">
-      <c r="A171" s="16" t="n"/>
-      <c r="B171" s="3" t="n"/>
-      <c r="C171" s="3" t="n"/>
-      <c r="E171" s="4" t="n"/>
-      <c r="F171" s="3" t="n"/>
-      <c r="G171" s="3" t="n"/>
+      <c r="A171" s="12" t="n">
+        <v>46193</v>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Carriage Outward</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Sote Phwar</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>စုပ်ဖွားဆေးပို့ကားခ(တပ်ကုန်း)</t>
+        </is>
+      </c>
+      <c r="F171" t="n">
+        <v>1508000</v>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>By Cash</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="K171" t="n">
+        <v>1806</v>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:01:31</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr"/>
     </row>
     <row r="172" ht="26" customHeight="1">
-      <c r="A172" s="16" t="n"/>
-      <c r="B172" s="3" t="n"/>
-      <c r="C172" s="3" t="n"/>
-      <c r="E172" s="4" t="n"/>
-      <c r="F172" s="3" t="n"/>
-      <c r="G172" s="3" t="n"/>
+      <c r="A172" s="12" t="n">
+        <v>46192</v>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Car Maintenance</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Sote Phwar</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Lucky Man မှ PROBOXအတွက်ပစ္စည်းဝယ်</t>
+        </is>
+      </c>
+      <c r="F172" t="n">
+        <v>12000</v>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>By Cash</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="K172" t="n">
+        <v>1807</v>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:01:31</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr"/>
     </row>
     <row r="173" ht="26" customHeight="1">
-      <c r="A173" s="16" t="n"/>
-      <c r="B173" s="3" t="n"/>
-      <c r="C173" s="3" t="n"/>
-      <c r="E173" s="3" t="n"/>
-      <c r="F173" s="3" t="n"/>
-      <c r="G173" s="3" t="n"/>
+      <c r="A173" s="12" t="n">
+        <v>46191</v>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Car Maintenance</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Sote Phwar</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Lucky Man မှ PROBOXအတွက်ပစ္စည်းဝယ်</t>
+        </is>
+      </c>
+      <c r="F173" t="n">
+        <v>1611000</v>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>By Cash</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="K173" t="n">
+        <v>1808</v>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:01:31</t>
+        </is>
+      </c>
+      <c r="M173" t="inlineStr"/>
     </row>
     <row r="174" ht="26" customHeight="1">
-      <c r="A174" s="16" t="n"/>
-      <c r="B174" s="3" t="n"/>
-      <c r="C174" s="3" t="n"/>
-      <c r="E174" s="3" t="n"/>
-      <c r="F174" s="3" t="n"/>
-      <c r="G174" s="3" t="n"/>
+      <c r="A174" s="12" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Car Maintenance</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Sote Phwar</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>iCar-18 မှ PROBOX(5F-3047)အတွက် ပစ္စည်းဝယ်</t>
+        </is>
+      </c>
+      <c r="F174" t="n">
+        <v>1432900</v>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>By Cash</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="K174" t="n">
+        <v>1809</v>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:01:31</t>
+        </is>
+      </c>
+      <c r="M174" t="inlineStr"/>
     </row>
     <row r="175" ht="26" customHeight="1">
-      <c r="A175" s="16" t="n"/>
-      <c r="B175" s="3" t="n"/>
-      <c r="C175" s="3" t="n"/>
-      <c r="E175" s="3" t="n"/>
-      <c r="F175" s="3" t="n"/>
-      <c r="G175" s="3" t="n"/>
+      <c r="A175" s="12" t="n">
+        <v>46191</v>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Machinery repair &amp; maintenance </t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Sote Phwar</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>ကားပရိုဘောက်အတွက်ပစ္စည်းဝယ်(5F-3047)</t>
+        </is>
+      </c>
+      <c r="F175" t="n">
+        <v>2026000</v>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>By Cash</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="K175" t="n">
+        <v>1810</v>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:01:31</t>
+        </is>
+      </c>
+      <c r="M175" t="inlineStr"/>
     </row>
     <row r="176" ht="26" customHeight="1">
-      <c r="A176" s="16" t="n"/>
-      <c r="B176" s="3" t="n"/>
-      <c r="C176" s="3" t="n"/>
-      <c r="E176" s="3" t="n"/>
-      <c r="F176" s="3" t="n"/>
-      <c r="G176" s="3" t="n"/>
+      <c r="A176" s="12" t="n">
+        <v>46192</v>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Carriage Outward</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Sote Phwar</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>စုပ်ဖွားဆေးပို့ကားခ</t>
+        </is>
+      </c>
+      <c r="F176" t="n">
+        <v>280000</v>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>By Cash</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="K176" t="n">
+        <v>1811</v>
+      </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:01:31</t>
+        </is>
+      </c>
+      <c r="M176" t="inlineStr"/>
     </row>
     <row r="177" ht="26" customHeight="1">
-      <c r="A177" s="16" t="n"/>
-      <c r="B177" s="3" t="n"/>
-      <c r="C177" s="3" t="n"/>
-      <c r="E177" s="3" t="n"/>
-      <c r="F177" s="3" t="n"/>
-      <c r="G177" s="3" t="n"/>
+      <c r="A177" s="12" t="n">
+        <v>46193</v>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Warehouse Maintenance Expense</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Sote Phwar</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>မီးပစ္စည်းဝယ်</t>
+        </is>
+      </c>
+      <c r="F177" t="n">
+        <v>4476600</v>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>By K-Pay</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="K177" t="n">
+        <v>1812</v>
+      </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:01:31</t>
+        </is>
+      </c>
+      <c r="M177" t="inlineStr"/>
     </row>
     <row r="178" ht="26" customHeight="1">
-      <c r="A178" s="16" t="n"/>
-      <c r="B178" s="3" t="n"/>
-      <c r="C178" s="3" t="n"/>
-      <c r="E178" s="3" t="n"/>
-      <c r="F178" s="3" t="n"/>
-      <c r="G178" s="3" t="n"/>
+      <c r="A178" s="12" t="n">
+        <v>46192</v>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Carriage Outward</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Sote Phwar</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>စုပ်ဖွား ဆေးပို့ကားခ</t>
+        </is>
+      </c>
+      <c r="F178" t="n">
+        <v>80000</v>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>By Cash</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="K178" t="n">
+        <v>1813</v>
+      </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:01:31</t>
+        </is>
+      </c>
+      <c r="M178" t="inlineStr"/>
     </row>
     <row r="179" ht="26" customHeight="1">
-      <c r="A179" s="16" t="n"/>
-      <c r="B179" s="3" t="n"/>
-      <c r="C179" s="3" t="n"/>
-      <c r="E179" s="3" t="n"/>
-      <c r="F179" s="3" t="n"/>
-      <c r="G179" s="3" t="n"/>
+      <c r="A179" s="12" t="n">
+        <v>46191</v>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Fuel</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Sote Phwar</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>95(ခွန်အောင်မိုး)</t>
+        </is>
+      </c>
+      <c r="F179" t="n">
+        <v>120000</v>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>By Cash</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="K179" t="n">
+        <v>1814</v>
+      </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:01:31</t>
+        </is>
+      </c>
+      <c r="M179" t="inlineStr"/>
     </row>
     <row r="180" ht="26" customHeight="1">
-      <c r="A180" s="16" t="n"/>
-      <c r="B180" s="3" t="n"/>
-      <c r="C180" s="3" t="n"/>
-      <c r="E180" s="3" t="n"/>
-      <c r="F180" s="3" t="n"/>
-      <c r="G180" s="3" t="n"/>
+      <c r="A180" s="12" t="n">
+        <v>46191</v>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Machinery repair &amp; maintenance </t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Sote Phwar</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Head အောက်သံပြားပြင်လက်ခ</t>
+        </is>
+      </c>
+      <c r="F180" t="n">
+        <v>20000</v>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>By Cash</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="K180" t="n">
+        <v>1815</v>
+      </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:01:31</t>
+        </is>
+      </c>
+      <c r="M180" t="inlineStr"/>
     </row>
     <row r="181" ht="26" customHeight="1">
-      <c r="A181" s="16" t="n"/>
-      <c r="B181" s="3" t="n"/>
-      <c r="C181" s="3" t="n"/>
-      <c r="E181" s="3" t="n"/>
-      <c r="F181" s="3" t="n"/>
-      <c r="G181" s="3" t="n"/>
+      <c r="A181" s="12" t="n">
+        <v>46191</v>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Warehouse Maintenance Expense</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Sote Phwar</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>မီးသီးဝယ်၊ကျောက်လှည့်၊ကတ္တာမာတီ</t>
+        </is>
+      </c>
+      <c r="F181" t="n">
+        <v>127000</v>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>By Cash</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="K181" t="n">
+        <v>1816</v>
+      </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:01:31</t>
+        </is>
+      </c>
+      <c r="M181" t="inlineStr"/>
     </row>
     <row r="182" ht="26" customHeight="1">
-      <c r="A182" s="16" t="n"/>
-      <c r="B182" s="3" t="n"/>
-      <c r="C182" s="3" t="n"/>
-      <c r="E182" s="3" t="n"/>
-      <c r="F182" s="3" t="n"/>
-      <c r="G182" s="3" t="n"/>
+      <c r="A182" s="12" t="n">
+        <v>46191</v>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Fuel</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Sote Phwar</t>
+        </is>
+      </c>
+      <c r="E182" t="n">
+        <v>95</v>
+      </c>
+      <c r="F182" t="n">
+        <v>12000</v>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>By Cash</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="K182" t="n">
+        <v>1817</v>
+      </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:01:31</t>
+        </is>
+      </c>
+      <c r="M182" t="inlineStr"/>
     </row>
     <row r="183" ht="26" customHeight="1">
-      <c r="A183" s="16" t="n"/>
-      <c r="B183" s="3" t="n"/>
-      <c r="C183" s="3" t="n"/>
-      <c r="E183" s="4" t="n"/>
-      <c r="F183" s="3" t="n"/>
-      <c r="G183" s="3" t="n"/>
+      <c r="A183" s="12" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Warehouse Maintenance Expense</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Sote Phwar</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>မီးပစ္စည်းဝယ်</t>
+        </is>
+      </c>
+      <c r="F183" t="n">
+        <v>170600</v>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>By Cash</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="K183" t="n">
+        <v>1818</v>
+      </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:01:31</t>
+        </is>
+      </c>
+      <c r="M183" t="inlineStr"/>
     </row>
     <row r="184" ht="26" customHeight="1">
-      <c r="A184" s="16" t="n"/>
-      <c r="B184" s="3" t="n"/>
-      <c r="C184" s="3" t="n"/>
-      <c r="E184" s="3" t="n"/>
-      <c r="F184" s="3" t="n"/>
-      <c r="G184" s="3" t="n"/>
+      <c r="A184" s="12" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Warehouse Maintenance Expense</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Sote Phwar</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>မီးပစ္စည်းဝယ်</t>
+        </is>
+      </c>
+      <c r="F184" t="n">
+        <v>93800</v>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>By Cash</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="K184" t="n">
+        <v>1819</v>
+      </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:01:31</t>
+        </is>
+      </c>
+      <c r="M184" t="inlineStr"/>
     </row>
     <row r="185" ht="26" customHeight="1">
-      <c r="A185" s="16" t="n"/>
-      <c r="B185" s="3" t="n"/>
-      <c r="C185" s="3" t="n"/>
-      <c r="E185" s="4" t="n"/>
-      <c r="F185" s="3" t="n"/>
-      <c r="G185" s="3" t="n"/>
+      <c r="A185" s="12" t="n">
+        <v>46189</v>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Molasses</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Sote Phwar</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>3071ပိဿာ*1300</t>
+        </is>
+      </c>
+      <c r="F185" t="n">
+        <v>3992300</v>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>By Cash</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="K185" t="n">
+        <v>1820</v>
+      </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:01:31</t>
+        </is>
+      </c>
+      <c r="M185" t="inlineStr"/>
     </row>
     <row r="186" ht="26" customHeight="1">
-      <c r="A186" s="16" t="n"/>
-      <c r="B186" s="3" t="n"/>
-      <c r="C186" s="3" t="n"/>
-      <c r="E186" s="3" t="n"/>
-      <c r="F186" s="3" t="n"/>
-      <c r="G186" s="3" t="n"/>
+      <c r="A186" s="12" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Fuel</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Sote Phwar</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Premium Diesel (1T/1918)</t>
+        </is>
+      </c>
+      <c r="F186" t="n">
+        <v>150000</v>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>By Cash</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="K186" t="n">
+        <v>1821</v>
+      </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:01:31</t>
+        </is>
+      </c>
+      <c r="M186" t="inlineStr"/>
     </row>
     <row r="187" ht="26" customHeight="1">
-      <c r="A187" s="16" t="n"/>
-      <c r="B187" s="3" t="n"/>
-      <c r="C187" s="3" t="n"/>
-      <c r="F187" s="3" t="n"/>
-      <c r="G187" s="3" t="n"/>
+      <c r="A187" s="12" t="n">
+        <v>46189</v>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Carriage Inward</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Sote Phwar</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>စုပ်ဖွားဂျပ်ဖာပို့ကားခ</t>
+        </is>
+      </c>
+      <c r="F187" t="n">
+        <v>263000</v>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>By Cash</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="K187" t="n">
+        <v>1822</v>
+      </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:01:31</t>
+        </is>
+      </c>
+      <c r="M187" t="inlineStr"/>
     </row>
     <row r="188" ht="26" customHeight="1">
-      <c r="A188" s="16" t="n"/>
-      <c r="B188" s="3" t="n"/>
-      <c r="C188" s="3" t="n"/>
-      <c r="F188" s="3" t="n"/>
-      <c r="G188" s="3" t="n"/>
+      <c r="A188" s="12" t="n">
+        <v>46189</v>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t xml:space="preserve">General Expense </t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Sote Phwar</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>လမ်းကြေး၊လေချိန်</t>
+        </is>
+      </c>
+      <c r="F188" t="n">
+        <v>20000</v>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>By Cash</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="K188" t="n">
+        <v>1823</v>
+      </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:01:31</t>
+        </is>
+      </c>
+      <c r="M188" t="inlineStr"/>
     </row>
     <row r="189" ht="26" customHeight="1">
-      <c r="A189" s="16" t="n"/>
-      <c r="B189" s="3" t="n"/>
-      <c r="C189" s="3" t="n"/>
-      <c r="E189" s="3" t="n"/>
-      <c r="F189" s="3" t="n"/>
-      <c r="G189" s="3" t="n"/>
+      <c r="A189" s="12" t="n">
+        <v>46189</v>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Packaging equipment</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Sote Phwar</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>ဘူးခွံစတေကာကပ် စာရင်း</t>
+        </is>
+      </c>
+      <c r="F189" t="n">
+        <v>162280</v>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>By Cash</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="K189" t="n">
+        <v>1824</v>
+      </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:01:31</t>
+        </is>
+      </c>
+      <c r="M189" t="inlineStr"/>
     </row>
     <row r="190">
-      <c r="A190" s="16" t="n"/>
-      <c r="B190" s="3" t="n"/>
-      <c r="C190" s="3" t="n"/>
-      <c r="E190" s="3" t="n"/>
-      <c r="F190" s="3" t="n"/>
-      <c r="G190" s="3" t="n"/>
+      <c r="A190" s="12" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Kitchen Expense</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Sote Phwar</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>မီးဖိုချောင်သုံးပစ္စည်း</t>
+        </is>
+      </c>
+      <c r="F190" t="n">
+        <v>757800</v>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>By K-Pay</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="K190" t="n">
+        <v>1825</v>
+      </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:01:31</t>
+        </is>
+      </c>
+      <c r="M190" t="inlineStr"/>
     </row>
     <row r="191" ht="26" customHeight="1">
-      <c r="A191" s="16" t="n"/>
-      <c r="B191" s="3" t="n"/>
-      <c r="C191" s="3" t="n"/>
-      <c r="E191" s="4" t="n"/>
-      <c r="F191" s="3" t="n"/>
-      <c r="G191" s="3" t="n"/>
+      <c r="A191" s="12" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Packaging equipment</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Sote Phwar</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>1L bigshot(B logo)</t>
+        </is>
+      </c>
+      <c r="F191" t="n">
+        <v>5966400</v>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>By K-Pay</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="K191" t="n">
+        <v>1826</v>
+      </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:01:31</t>
+        </is>
+      </c>
+      <c r="M191" t="inlineStr"/>
     </row>
     <row r="192" ht="26" customHeight="1">
-      <c r="A192" s="16" t="n"/>
-      <c r="B192" s="3" t="n"/>
-      <c r="C192" s="3" t="n"/>
-      <c r="E192" s="4" t="n"/>
-      <c r="F192" s="3" t="n"/>
-      <c r="G192" s="3" t="n"/>
+      <c r="A192" s="12" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Carriage Inward</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Sote Phwar</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>ဗူးခွံကားခ</t>
+        </is>
+      </c>
+      <c r="F192" t="n">
+        <v>105000</v>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>By Cash</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="K192" t="n">
+        <v>1827</v>
+      </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:01:31</t>
+        </is>
+      </c>
+      <c r="M192" t="inlineStr"/>
     </row>
     <row r="193">
-      <c r="A193" s="16" t="n"/>
-      <c r="B193" s="3" t="n"/>
-      <c r="C193" s="3" t="n"/>
-      <c r="E193" s="3" t="n"/>
-      <c r="F193" s="3" t="n"/>
-      <c r="G193" s="3" t="n"/>
+      <c r="A193" s="12" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Car Maintenance</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Sote Phwar</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>ကားအောက်ပိုင်းပြုပြင်ခြင်း</t>
+        </is>
+      </c>
+      <c r="F193" t="n">
+        <v>7199500</v>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>By Cash</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="K193" t="n">
+        <v>1828</v>
+      </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:01:31</t>
+        </is>
+      </c>
+      <c r="M193" t="inlineStr"/>
     </row>
     <row r="194" ht="26" customHeight="1">
-      <c r="A194" s="16" t="n"/>
-      <c r="B194" s="3" t="n"/>
-      <c r="C194" s="3" t="n"/>
-      <c r="E194" s="3" t="n"/>
-      <c r="F194" s="3" t="n"/>
-      <c r="G194" s="3" t="n"/>
+      <c r="A194" s="12" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Warehouse Maintenance Expense</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Sote Phwar</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>ATM ရေဆေး ဖြူ(1G)</t>
+        </is>
+      </c>
+      <c r="F194" t="n">
+        <v>101500</v>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>By Cash</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="K194" t="n">
+        <v>1829</v>
+      </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:01:31</t>
+        </is>
+      </c>
+      <c r="M194" t="inlineStr"/>
     </row>
     <row r="195">
-      <c r="A195" s="16" t="n"/>
-      <c r="B195" s="3" t="n"/>
-      <c r="C195" s="3" t="n"/>
-      <c r="E195" s="3" t="n"/>
-      <c r="F195" s="3" t="n"/>
-      <c r="G195" s="3" t="n"/>
+      <c r="A195" s="12" t="n">
+        <v>46177</v>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Factory 2 Set up cost</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Sote Phwar</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>ဆောက်လုပ်ရေးပစ္စည်း</t>
+        </is>
+      </c>
+      <c r="F195" t="n">
+        <v>162430</v>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>By Cash</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="K195" t="n">
+        <v>1830</v>
+      </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:01:31</t>
+        </is>
+      </c>
+      <c r="M195" t="inlineStr"/>
     </row>
     <row r="196" ht="26" customHeight="1">
-      <c r="A196" s="16" t="n"/>
-      <c r="B196" s="3" t="n"/>
-      <c r="C196" s="3" t="n"/>
-      <c r="E196" s="4" t="n"/>
-      <c r="F196" s="3" t="n"/>
-      <c r="G196" s="3" t="n"/>
+      <c r="A196" s="12" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Molasses</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Sote Phwar</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>2875 ပိဿာ*1300</t>
+        </is>
+      </c>
+      <c r="F196" t="n">
+        <v>3737500</v>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>By Cash</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="K196" t="n">
+        <v>1831</v>
+      </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:01:31</t>
+        </is>
+      </c>
+      <c r="M196" t="inlineStr"/>
     </row>
     <row r="197" ht="26" customHeight="1">
-      <c r="A197" s="16" t="n"/>
-      <c r="B197" s="3" t="n"/>
-      <c r="C197" s="3" t="n"/>
-      <c r="E197" s="4" t="n"/>
-      <c r="F197" s="3" t="n"/>
-      <c r="G197" s="3" t="n"/>
+      <c r="A197" s="12" t="n">
+        <v>46180</v>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Stationaries &amp; Admin Expenses</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Sote Phwar</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>Photo Sticker ၊ Glycer ၊Paper Clips</t>
+        </is>
+      </c>
+      <c r="F197" t="n">
+        <v>127500</v>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>By Cash</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="K197" t="n">
+        <v>1832</v>
+      </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:01:31</t>
+        </is>
+      </c>
+      <c r="M197" t="inlineStr"/>
     </row>
     <row r="198" ht="26" customHeight="1">
       <c r="A198" s="16" t="n"/>
@@ -12680,7 +16073,6 @@
           <t>2026-06-19 14:23:24</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="6" t="n">
@@ -12722,7 +16114,6 @@
           <t>2026-06-19 14:23:24</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="6" t="n">
@@ -12764,7 +16155,6 @@
           <t>2026-06-19 14:23:24</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="6" t="n">
@@ -12806,7 +16196,6 @@
           <t>2026-06-19 14:23:24</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="6" t="n">
@@ -12848,7 +16237,6 @@
           <t>2026-06-19 14:23:24</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="6" t="n">
@@ -12890,7 +16278,6 @@
           <t>2026-06-19 14:23:24</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="6" t="n">
@@ -12932,7 +16319,6 @@
           <t>2026-06-19 14:23:24</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="6" t="n">
@@ -12974,7 +16360,6 @@
           <t>2026-06-19 14:23:24</t>
         </is>
       </c>
-      <c r="N54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="6" t="n">
@@ -13020,7 +16405,6 @@
           <t>2026-06-19 14:23:24</t>
         </is>
       </c>
-      <c r="N55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="6" t="n">
@@ -13066,7 +16450,6 @@
           <t>2026-06-19 14:23:24</t>
         </is>
       </c>
-      <c r="N56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="6" t="n">
@@ -13112,7 +16495,6 @@
           <t>2026-06-19 14:23:24</t>
         </is>
       </c>
-      <c r="N57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="6" t="n">
@@ -13158,7 +16540,6 @@
           <t>2026-06-19 14:23:24</t>
         </is>
       </c>
-      <c r="N58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="6" t="n">
@@ -13200,7 +16581,6 @@
           <t>2026-06-19 14:23:24</t>
         </is>
       </c>
-      <c r="N59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="6" t="n">
@@ -13242,7 +16622,6 @@
           <t>2026-06-19 14:23:24</t>
         </is>
       </c>
-      <c r="N60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="6" t="n">
@@ -13284,7 +16663,6 @@
           <t>2026-06-19 14:23:24</t>
         </is>
       </c>
-      <c r="N61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="6" t="n">
@@ -13326,7 +16704,6 @@
           <t>2026-06-19 14:23:24</t>
         </is>
       </c>
-      <c r="N62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="6" t="n">
@@ -13368,7 +16745,6 @@
           <t>2026-06-19 14:23:24</t>
         </is>
       </c>
-      <c r="N63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="6" t="n">
@@ -13410,7 +16786,6 @@
           <t>2026-06-19 14:23:24</t>
         </is>
       </c>
-      <c r="N64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="6" t="n">
@@ -13452,7 +16827,6 @@
           <t>2026-06-19 14:23:24</t>
         </is>
       </c>
-      <c r="N65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="6" t="n">
@@ -13494,7 +16868,6 @@
           <t>2026-06-19 14:23:24</t>
         </is>
       </c>
-      <c r="N66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="6" t="n">
@@ -13536,7 +16909,6 @@
           <t>2026-06-19 14:23:24</t>
         </is>
       </c>
-      <c r="N67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="6" t="n">
@@ -13578,7 +16950,6 @@
           <t>2026-06-19 14:23:24</t>
         </is>
       </c>
-      <c r="N68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="6" t="n">
@@ -13620,7 +16991,6 @@
           <t>2026-06-19 14:23:24</t>
         </is>
       </c>
-      <c r="N69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="6" t="n">
@@ -13662,7 +17032,6 @@
           <t>2026-06-19 14:23:24</t>
         </is>
       </c>
-      <c r="N70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="6" t="n">
@@ -13704,7 +17073,6 @@
           <t>2026-06-19 14:23:24</t>
         </is>
       </c>
-      <c r="N71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="6" t="n">
@@ -13746,7 +17114,6 @@
           <t>2026-06-19 14:23:24</t>
         </is>
       </c>
-      <c r="N72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="6" t="n">
@@ -13788,7 +17155,6 @@
           <t>2026-06-19 14:23:24</t>
         </is>
       </c>
-      <c r="N73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="6" t="n">
@@ -13830,7 +17196,6 @@
           <t>2026-06-19 14:23:24</t>
         </is>
       </c>
-      <c r="N74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="6" t="n">
@@ -13872,7 +17237,6 @@
           <t>2026-06-19 14:23:24</t>
         </is>
       </c>
-      <c r="N75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="6" t="n">
@@ -13914,7 +17278,6 @@
           <t>2026-06-19 14:23:24</t>
         </is>
       </c>
-      <c r="N76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="6" t="n">
@@ -13956,7 +17319,6 @@
           <t>2026-06-19 14:23:24</t>
         </is>
       </c>
-      <c r="N77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="6" t="n">
@@ -13998,7 +17360,6 @@
           <t>2026-06-19 14:23:24</t>
         </is>
       </c>
-      <c r="N78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="6" t="n">
@@ -14040,7 +17401,6 @@
           <t>2026-06-19 14:23:24</t>
         </is>
       </c>
-      <c r="N79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="6" t="n">
@@ -14082,7 +17442,6 @@
           <t>2026-06-19 14:23:24</t>
         </is>
       </c>
-      <c r="N80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="6" t="n">
@@ -14124,7 +17483,6 @@
           <t>2026-06-19 14:23:24</t>
         </is>
       </c>
-      <c r="N81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="6" t="n">
@@ -14166,7 +17524,6 @@
           <t>2026-06-19 14:23:24</t>
         </is>
       </c>
-      <c r="N82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="6" t="n">
@@ -14212,7 +17569,6 @@
           <t>2026-06-19 14:23:24</t>
         </is>
       </c>
-      <c r="N83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="6" t="n">
@@ -14254,7 +17610,6 @@
           <t>2026-06-19 14:23:24</t>
         </is>
       </c>
-      <c r="N84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="6" t="n">
@@ -14296,7 +17651,6 @@
           <t>2026-06-19 14:23:24</t>
         </is>
       </c>
-      <c r="N85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="6" t="n">
@@ -14338,7 +17692,6 @@
           <t>2026-06-19 14:23:24</t>
         </is>
       </c>
-      <c r="N86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="6" t="n">
@@ -14380,7 +17733,6 @@
           <t>2026-06-19 14:23:24</t>
         </is>
       </c>
-      <c r="N87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="6" t="n">
@@ -14422,7 +17774,6 @@
           <t>2026-06-19 14:23:24</t>
         </is>
       </c>
-      <c r="N88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="6" t="n"/>

--- a/excel_import/business_data_import_template.xlsx
+++ b/excel_import/business_data_import_template.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19380" tabRatio="600" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19300" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
@@ -10078,88 +10078,928 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n"/>
+      <c r="A2" s="3" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Makro</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>77</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2786200</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2786200</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>130</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2026-07-23 21:13:50</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n"/>
+      <c r="A3" s="3" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Makro</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>78</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1843100</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1843100</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>131</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2026-07-23 21:13:50</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n"/>
+      <c r="A4" s="3" t="n">
+        <v>46191</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Makro</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>79</v>
+      </c>
+      <c r="D4" t="n">
+        <v>3375000</v>
+      </c>
+      <c r="E4" t="n">
+        <v>3375000</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>132</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2026-07-23 21:13:50</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n"/>
+      <c r="A5" s="3" t="n">
+        <v>46191</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Makro</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>80</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1990900</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1990900</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>133</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2026-07-23 21:13:50</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n"/>
+      <c r="A6" s="3" t="n">
+        <v>46195</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Makro</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>81</v>
+      </c>
+      <c r="D6" t="n">
+        <v>3633000</v>
+      </c>
+      <c r="E6" t="n">
+        <v>3633000</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>134</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2026-07-23 21:13:50</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n"/>
+      <c r="A7" s="3" t="n">
+        <v>46195</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Makro</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>82</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2118200</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2118200</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>135</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2026-07-23 21:13:50</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n"/>
+      <c r="A8" s="3" t="n">
+        <v>46198</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Makro</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>83</v>
+      </c>
+      <c r="D8" t="n">
+        <v>3108000</v>
+      </c>
+      <c r="E8" t="n">
+        <v>3108000</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>136</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2026-07-23 21:13:50</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n"/>
+      <c r="A9" s="3" t="n">
+        <v>46198</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Makro</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>84</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1778800</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1778800</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>137</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2026-07-23 21:13:50</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n"/>
+      <c r="A10" s="3" t="n">
+        <v>46202</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Makro</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>85</v>
+      </c>
+      <c r="D10" t="n">
+        <v>3384500</v>
+      </c>
+      <c r="E10" t="n">
+        <v>3384500</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>138</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>2026-07-23 21:13:50</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n"/>
+      <c r="A11" s="3" t="n">
+        <v>46202</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Makro</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>86</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2087000</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2087000</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>139</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2026-07-23 21:13:50</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n"/>
+      <c r="A12" s="3" t="n">
+        <v>46205</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Makro</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>87</v>
+      </c>
+      <c r="D12" t="n">
+        <v>3523200</v>
+      </c>
+      <c r="E12" t="n">
+        <v>3523200</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>140</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2026-07-23 21:13:50</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n"/>
+      <c r="A13" s="3" t="n">
+        <v>46205</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Makro</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>88</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2610500</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2610500</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>141</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>2026-07-23 21:13:50</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n"/>
+      <c r="A14" s="3" t="n">
+        <v>46209</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Makro</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>89</v>
+      </c>
+      <c r="D14" t="n">
+        <v>3747000</v>
+      </c>
+      <c r="E14" t="n">
+        <v>3747000</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>142</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>2026-07-23 21:13:50</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n"/>
+      <c r="A15" s="3" t="n">
+        <v>46209</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Makro</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>90</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2858000</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2858000</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>143</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>2026-07-23 21:13:50</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n"/>
+      <c r="A16" s="3" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Makro</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>91</v>
+      </c>
+      <c r="D16" t="n">
+        <v>3263000</v>
+      </c>
+      <c r="E16" t="n">
+        <v>3263000</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>144</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>2026-07-23 21:13:50</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n"/>
+      <c r="A17" s="3" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Makro</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>92</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2707500</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2707500</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>145</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>2026-07-23 21:13:50</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n"/>
+      <c r="A18" s="3" t="n">
+        <v>46216</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Makro</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>93</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2661000</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2661000</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>146</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>2026-07-23 21:13:50</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n"/>
+      <c r="A19" s="3" t="n">
+        <v>46216</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Makro</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>94</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1899900</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1899900</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>147</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>2026-07-23 21:13:50</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n"/>
+      <c r="A20" s="3" t="n">
+        <v>46216</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Makro</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>95</v>
+      </c>
+      <c r="D20" t="n">
+        <v>968000</v>
+      </c>
+      <c r="E20" t="n">
+        <v>968000</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>148</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>2026-07-23 21:13:50</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n"/>
+      <c r="A21" s="3" t="n">
+        <v>46216</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Makro</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>96</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1284000</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1284000</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>149</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>2026-07-23 21:13:50</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n"/>
+      <c r="A22" s="3" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Makro</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>97</v>
+      </c>
+      <c r="D22" t="n">
+        <v>3414700</v>
+      </c>
+      <c r="E22" t="n">
+        <v>3414700</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>150</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>2026-07-23 21:13:50</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n"/>
+      <c r="A23" s="3" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Makro</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>98</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1937400</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1937400</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>151</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>2026-07-23 21:13:50</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n"/>
+      <c r="A24" s="3" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Makro</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>99</v>
+      </c>
+      <c r="D24" t="n">
+        <v>184000</v>
+      </c>
+      <c r="E24" t="n">
+        <v>184000</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>152</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>2026-07-23 21:13:50</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n"/>
+      <c r="A25" s="3" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Makro</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>100</v>
+      </c>
+      <c r="D25" t="n">
+        <v>92000</v>
+      </c>
+      <c r="E25" t="n">
+        <v>92000</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>153</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>2026-07-23 21:13:50</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n"/>
+      <c r="A26" s="3" t="n">
+        <v>46223</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Makro</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>101</v>
+      </c>
+      <c r="D26" t="n">
+        <v>3517500</v>
+      </c>
+      <c r="E26" t="n">
+        <v>3517500</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>154</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>2026-07-23 21:13:50</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n"/>
+      <c r="A27" s="3" t="n">
+        <v>46223</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Makro</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>102</v>
+      </c>
+      <c r="D27" t="n">
+        <v>2196400</v>
+      </c>
+      <c r="E27" t="n">
+        <v>2196400</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>155</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>2026-07-23 21:13:50</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n"/>
+      <c r="A28" s="3" t="n">
+        <v>46226</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Makro</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>103</v>
+      </c>
+      <c r="D28" t="n">
+        <v>4703500</v>
+      </c>
+      <c r="E28" t="n">
+        <v>4703500</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>156</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>2026-07-23 21:13:50</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n"/>
+      <c r="A29" s="3" t="n">
+        <v>46226</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Makro</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>104</v>
+      </c>
+      <c r="D29" t="n">
+        <v>2410400</v>
+      </c>
+      <c r="E29" t="n">
+        <v>2410400</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>INSERTED</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>157</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>2026-07-23 21:13:50</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n"/>
@@ -10752,7 +11592,6 @@
           <t>2026-07-21 00:32:05</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -10802,7 +11641,6 @@
           <t>2026-07-21 00:32:05</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
